--- a/artfynd/A 47636-2022 artfynd.xlsx
+++ b/artfynd/A 47636-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120046564</v>
+        <v>120046580</v>
       </c>
       <c r="B2" t="n">
-        <v>91547</v>
+        <v>97928</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,26 +691,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5836</v>
+        <v>221952</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Guldkremla</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Russula aurea</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Pers.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>454274</v>
+        <v>454254</v>
       </c>
       <c r="R2" t="n">
-        <v>7170002</v>
+        <v>7169982</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -892,10 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120046880</v>
+        <v>120046869</v>
       </c>
       <c r="B4" t="n">
-        <v>97928</v>
+        <v>97907</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,25 +905,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -999,10 +1000,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120046948</v>
+        <v>120046626</v>
       </c>
       <c r="B5" t="n">
-        <v>97930</v>
+        <v>104994</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1015,21 +1016,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219847</v>
+        <v>221725</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1043,10 +1044,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>454190</v>
+        <v>454185</v>
       </c>
       <c r="R5" t="n">
-        <v>7170110</v>
+        <v>7169988</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1106,10 +1107,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120046486</v>
+        <v>120046814</v>
       </c>
       <c r="B6" t="n">
-        <v>94311</v>
+        <v>78526</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1118,31 +1119,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2809</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1150,10 +1150,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454316</v>
+        <v>454172</v>
       </c>
       <c r="R6" t="n">
-        <v>7169955</v>
+        <v>7170015</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1186,6 +1186,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-08-18</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På grangrenar.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1213,10 +1218,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120046446</v>
+        <v>120046880</v>
       </c>
       <c r="B7" t="n">
-        <v>78526</v>
+        <v>97928</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1225,30 +1230,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1256,10 +1262,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>454357</v>
+        <v>454180</v>
       </c>
       <c r="R7" t="n">
-        <v>7169950</v>
+        <v>7170065</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1292,11 +1298,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-08-18</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På grangrenar.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1324,10 +1325,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120046580</v>
+        <v>120046602</v>
       </c>
       <c r="B8" t="n">
-        <v>97928</v>
+        <v>90527</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1340,27 +1341,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221952</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1368,10 +1368,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>454254</v>
+        <v>454188</v>
       </c>
       <c r="R8" t="n">
-        <v>7169982</v>
+        <v>7169986</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1404,6 +1404,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-08-18</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På granhögstubbe.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1431,10 +1436,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120046421</v>
+        <v>120046446</v>
       </c>
       <c r="B9" t="n">
-        <v>98242</v>
+        <v>78526</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1443,31 +1448,30 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219880</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1475,10 +1479,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>454365</v>
+        <v>454357</v>
       </c>
       <c r="R9" t="n">
-        <v>7169956</v>
+        <v>7169950</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1511,6 +1515,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-08-18</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På grangrenar.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1538,10 +1547,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120046602</v>
+        <v>120046564</v>
       </c>
       <c r="B10" t="n">
-        <v>90527</v>
+        <v>91547</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1554,21 +1563,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>5836</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Guldkremla</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Russula aurea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Pers.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1581,10 +1590,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>454188</v>
+        <v>454274</v>
       </c>
       <c r="R10" t="n">
-        <v>7169986</v>
+        <v>7170002</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1617,11 +1626,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-08-18</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>På granhögstubbe.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1649,10 +1653,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120046720</v>
+        <v>120046528</v>
       </c>
       <c r="B11" t="n">
-        <v>90558</v>
+        <v>97806</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1661,30 +1665,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1108</v>
+        <v>219795</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1692,10 +1697,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>454158</v>
+        <v>454297</v>
       </c>
       <c r="R11" t="n">
-        <v>7169997</v>
+        <v>7169982</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1728,11 +1733,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-08-18</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>På torrgran.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1760,10 +1760,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120046626</v>
+        <v>120046676</v>
       </c>
       <c r="B12" t="n">
-        <v>104994</v>
+        <v>74643</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1772,31 +1772,30 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221725</v>
+        <v>1467</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1804,10 +1803,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>454185</v>
+        <v>454160</v>
       </c>
       <c r="R12" t="n">
-        <v>7169988</v>
+        <v>7169971</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1840,6 +1839,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-08-18</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På högstubbe av björk.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1867,10 +1871,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120046876</v>
+        <v>120046842</v>
       </c>
       <c r="B13" t="n">
-        <v>97806</v>
+        <v>94251</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1883,21 +1887,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219795</v>
+        <v>756</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Käppkrokmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Hamatocaulis vernicosus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
+          <t>(Mitt.) Hedenäs</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1911,10 +1915,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>454180</v>
+        <v>454168</v>
       </c>
       <c r="R13" t="n">
-        <v>7170065</v>
+        <v>7170020</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1974,10 +1978,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120046869</v>
+        <v>120046632</v>
       </c>
       <c r="B14" t="n">
-        <v>97907</v>
+        <v>97824</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1986,25 +1990,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2018,10 +2022,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>454180</v>
+        <v>454185</v>
       </c>
       <c r="R14" t="n">
-        <v>7170065</v>
+        <v>7169988</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2081,10 +2085,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120046814</v>
+        <v>120046668</v>
       </c>
       <c r="B15" t="n">
-        <v>78526</v>
+        <v>79608</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2097,21 +2101,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2124,10 +2128,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>454172</v>
+        <v>454160</v>
       </c>
       <c r="R15" t="n">
-        <v>7170015</v>
+        <v>7169971</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2164,7 +2168,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På grangrenar.</t>
+          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2192,10 +2196,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120046676</v>
+        <v>120046486</v>
       </c>
       <c r="B16" t="n">
-        <v>74643</v>
+        <v>94311</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2204,30 +2208,31 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1467</v>
+        <v>2809</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2235,10 +2240,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>454160</v>
+        <v>454316</v>
       </c>
       <c r="R16" t="n">
-        <v>7169971</v>
+        <v>7169955</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2271,11 +2276,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-08-18</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På högstubbe av björk.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2303,10 +2303,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120046587</v>
+        <v>120046720</v>
       </c>
       <c r="B17" t="n">
-        <v>91494</v>
+        <v>90558</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2315,25 +2315,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4769</v>
+        <v>1108</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2346,10 +2346,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>454254</v>
+        <v>454158</v>
       </c>
       <c r="R17" t="n">
-        <v>7169982</v>
+        <v>7169997</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2382,6 +2382,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-08-18</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På torrgran.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2409,10 +2414,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120046702</v>
+        <v>120046554</v>
       </c>
       <c r="B18" t="n">
-        <v>78526</v>
+        <v>79636</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2421,25 +2426,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2452,10 +2457,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>454157</v>
+        <v>454274</v>
       </c>
       <c r="R18" t="n">
-        <v>7169992</v>
+        <v>7170002</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2492,7 +2497,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På grangrenar.</t>
+          <t>På klen rönn.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2520,10 +2525,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120046554</v>
+        <v>120046702</v>
       </c>
       <c r="B19" t="n">
-        <v>79636</v>
+        <v>78526</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2532,25 +2537,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2563,10 +2568,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>454274</v>
+        <v>454157</v>
       </c>
       <c r="R19" t="n">
-        <v>7170002</v>
+        <v>7169992</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2603,7 +2608,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På klen rönn.</t>
+          <t>På grangrenar.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2631,10 +2636,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120046528</v>
+        <v>120046420</v>
       </c>
       <c r="B20" t="n">
-        <v>97806</v>
+        <v>78526</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2643,31 +2648,30 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219795</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2675,10 +2679,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>454297</v>
+        <v>454365</v>
       </c>
       <c r="R20" t="n">
-        <v>7169982</v>
+        <v>7169956</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2711,6 +2715,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-08-18</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>På gammal björk.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2738,10 +2747,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120046472</v>
+        <v>120046948</v>
       </c>
       <c r="B21" t="n">
-        <v>97928</v>
+        <v>97930</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2754,21 +2763,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221952</v>
+        <v>219847</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2782,10 +2791,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>454355</v>
+        <v>454190</v>
       </c>
       <c r="R21" t="n">
-        <v>7169944</v>
+        <v>7170110</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2952,10 +2961,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120046842</v>
+        <v>120046472</v>
       </c>
       <c r="B23" t="n">
-        <v>94251</v>
+        <v>97928</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2968,21 +2977,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>756</v>
+        <v>221952</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Käppkrokmossa</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hamatocaulis vernicosus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Mitt.) Hedenäs</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2996,10 +3005,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>454168</v>
+        <v>454355</v>
       </c>
       <c r="R23" t="n">
-        <v>7170020</v>
+        <v>7169944</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3170,10 +3179,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120046632</v>
+        <v>120046587</v>
       </c>
       <c r="B25" t="n">
-        <v>97824</v>
+        <v>91494</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3186,27 +3195,26 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>219790</v>
+        <v>4769</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3214,10 +3222,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>454185</v>
+        <v>454254</v>
       </c>
       <c r="R25" t="n">
-        <v>7169988</v>
+        <v>7169982</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3277,10 +3285,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120046668</v>
+        <v>120046421</v>
       </c>
       <c r="B26" t="n">
-        <v>79608</v>
+        <v>98242</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3289,30 +3297,31 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2081</v>
+        <v>219880</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3320,10 +3329,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>454160</v>
+        <v>454365</v>
       </c>
       <c r="R26" t="n">
-        <v>7169971</v>
+        <v>7169956</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3356,11 +3365,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-08-18</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3388,10 +3392,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120046420</v>
+        <v>120046876</v>
       </c>
       <c r="B27" t="n">
-        <v>78526</v>
+        <v>97806</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3400,30 +3404,31 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>219795</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3431,10 +3436,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>454365</v>
+        <v>454180</v>
       </c>
       <c r="R27" t="n">
-        <v>7169956</v>
+        <v>7170065</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3467,11 +3472,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-08-18</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>På gammal björk.</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 47636-2022 artfynd.xlsx
+++ b/artfynd/A 47636-2022 artfynd.xlsx
@@ -1436,10 +1436,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120046446</v>
+        <v>120046564</v>
       </c>
       <c r="B9" t="n">
-        <v>78526</v>
+        <v>91547</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1448,25 +1448,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>5836</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Guldkremla</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Russula aurea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pers.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1479,10 +1479,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>454357</v>
+        <v>454274</v>
       </c>
       <c r="R9" t="n">
-        <v>7169950</v>
+        <v>7170002</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1515,11 +1515,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-08-18</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På grangrenar.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1547,10 +1542,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120046564</v>
+        <v>120046446</v>
       </c>
       <c r="B10" t="n">
-        <v>91547</v>
+        <v>78526</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1559,25 +1554,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5836</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Guldkremla</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Russula aurea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Pers.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1590,10 +1585,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>454274</v>
+        <v>454357</v>
       </c>
       <c r="R10" t="n">
-        <v>7170002</v>
+        <v>7169950</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1626,6 +1621,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-08-18</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På grangrenar.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1978,10 +1978,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120046632</v>
+        <v>120046668</v>
       </c>
       <c r="B14" t="n">
-        <v>97824</v>
+        <v>79608</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1990,31 +1990,30 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219790</v>
+        <v>2081</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2022,10 +2021,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>454185</v>
+        <v>454160</v>
       </c>
       <c r="R14" t="n">
-        <v>7169988</v>
+        <v>7169971</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2058,6 +2057,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-08-18</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2085,10 +2089,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120046668</v>
+        <v>120046486</v>
       </c>
       <c r="B15" t="n">
-        <v>79608</v>
+        <v>94311</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2097,30 +2101,31 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2081</v>
+        <v>2809</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2128,10 +2133,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>454160</v>
+        <v>454316</v>
       </c>
       <c r="R15" t="n">
-        <v>7169971</v>
+        <v>7169955</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2164,11 +2169,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-08-18</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2196,10 +2196,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120046486</v>
+        <v>120046632</v>
       </c>
       <c r="B16" t="n">
-        <v>94311</v>
+        <v>97824</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2212,21 +2212,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2809</v>
+        <v>219790</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2240,10 +2240,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>454316</v>
+        <v>454185</v>
       </c>
       <c r="R16" t="n">
-        <v>7169955</v>
+        <v>7169988</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2525,10 +2525,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120046702</v>
+        <v>120046845</v>
       </c>
       <c r="B19" t="n">
-        <v>78526</v>
+        <v>93743</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2537,30 +2537,31 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>2412</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Källmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Philonotis fontana</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2568,10 +2569,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>454157</v>
+        <v>454168</v>
       </c>
       <c r="R19" t="n">
-        <v>7169992</v>
+        <v>7170020</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2604,11 +2605,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-08-18</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På grangrenar.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2636,7 +2632,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120046420</v>
+        <v>120046702</v>
       </c>
       <c r="B20" t="n">
         <v>78526</v>
@@ -2679,10 +2675,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>454365</v>
+        <v>454157</v>
       </c>
       <c r="R20" t="n">
-        <v>7169956</v>
+        <v>7169992</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2719,7 +2715,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På gammal björk.</t>
+          <t>På grangrenar.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2747,10 +2743,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120046948</v>
+        <v>120046420</v>
       </c>
       <c r="B21" t="n">
-        <v>97930</v>
+        <v>78526</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2759,31 +2755,30 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219847</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2791,10 +2786,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>454190</v>
+        <v>454365</v>
       </c>
       <c r="R21" t="n">
-        <v>7170110</v>
+        <v>7169956</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2827,6 +2822,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-08-18</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På gammal björk.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2854,10 +2854,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120046845</v>
+        <v>120046948</v>
       </c>
       <c r="B22" t="n">
-        <v>93743</v>
+        <v>97930</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2870,21 +2870,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2412</v>
+        <v>219847</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Källmossa</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Philonotis fontana</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2898,10 +2898,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>454168</v>
+        <v>454190</v>
       </c>
       <c r="R22" t="n">
-        <v>7170020</v>
+        <v>7170110</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>

--- a/artfynd/A 47636-2022 artfynd.xlsx
+++ b/artfynd/A 47636-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120046580</v>
+        <v>120046676</v>
       </c>
       <c r="B2" t="n">
-        <v>97928</v>
+        <v>74643</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221952</v>
+        <v>1467</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>454254</v>
+        <v>454160</v>
       </c>
       <c r="R2" t="n">
-        <v>7169982</v>
+        <v>7169971</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -755,6 +754,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-08-18</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På högstubbe av björk.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120046671</v>
+        <v>120046948</v>
       </c>
       <c r="B3" t="n">
-        <v>79636</v>
+        <v>97930</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,26 +802,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>219847</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -825,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>454160</v>
+        <v>454190</v>
       </c>
       <c r="R3" t="n">
-        <v>7169971</v>
+        <v>7170110</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -861,11 +866,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-08-18</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,10 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120046869</v>
+        <v>120046845</v>
       </c>
       <c r="B4" t="n">
-        <v>97907</v>
+        <v>93743</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,25 +905,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>2412</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Källmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Philonotis fontana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>454180</v>
+        <v>454168</v>
       </c>
       <c r="R4" t="n">
-        <v>7170065</v>
+        <v>7170020</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1000,10 +1000,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120046626</v>
+        <v>120046876</v>
       </c>
       <c r="B5" t="n">
-        <v>104994</v>
+        <v>97806</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1016,21 +1016,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221725</v>
+        <v>219795</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1044,10 +1044,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>454185</v>
+        <v>454180</v>
       </c>
       <c r="R5" t="n">
-        <v>7169988</v>
+        <v>7170065</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1107,7 +1107,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120046814</v>
+        <v>120046446</v>
       </c>
       <c r="B6" t="n">
         <v>78526</v>
@@ -1150,10 +1150,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454172</v>
+        <v>454357</v>
       </c>
       <c r="R6" t="n">
-        <v>7170015</v>
+        <v>7169950</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1218,10 +1218,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120046880</v>
+        <v>120046421</v>
       </c>
       <c r="B7" t="n">
-        <v>97928</v>
+        <v>98242</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1234,21 +1234,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221952</v>
+        <v>219880</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1262,10 +1262,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>454180</v>
+        <v>454365</v>
       </c>
       <c r="R7" t="n">
-        <v>7170065</v>
+        <v>7169956</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1325,10 +1325,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120046602</v>
+        <v>120046528</v>
       </c>
       <c r="B8" t="n">
-        <v>90527</v>
+        <v>97806</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1341,26 +1341,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>219795</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1368,10 +1369,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>454188</v>
+        <v>454297</v>
       </c>
       <c r="R8" t="n">
-        <v>7169986</v>
+        <v>7169982</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1404,11 +1405,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-08-18</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På granhögstubbe.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1436,10 +1432,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120046564</v>
+        <v>120046602</v>
       </c>
       <c r="B9" t="n">
-        <v>91547</v>
+        <v>90527</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1452,21 +1448,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5836</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Guldkremla</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Russula aurea</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Pers.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1479,10 +1475,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>454274</v>
+        <v>454188</v>
       </c>
       <c r="R9" t="n">
-        <v>7170002</v>
+        <v>7169986</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1515,6 +1511,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-08-18</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På granhögstubbe.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1542,10 +1543,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120046446</v>
+        <v>120046554</v>
       </c>
       <c r="B10" t="n">
-        <v>78526</v>
+        <v>79636</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1554,25 +1555,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1585,10 +1586,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>454357</v>
+        <v>454274</v>
       </c>
       <c r="R10" t="n">
-        <v>7169950</v>
+        <v>7170002</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1625,7 +1626,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På grangrenar.</t>
+          <t>På klen rönn.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1653,10 +1654,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120046528</v>
+        <v>120046626</v>
       </c>
       <c r="B11" t="n">
-        <v>97806</v>
+        <v>104994</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1669,21 +1670,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219795</v>
+        <v>221725</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1697,10 +1698,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>454297</v>
+        <v>454185</v>
       </c>
       <c r="R11" t="n">
-        <v>7169982</v>
+        <v>7169988</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1760,10 +1761,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120046676</v>
+        <v>120046814</v>
       </c>
       <c r="B12" t="n">
-        <v>74643</v>
+        <v>78526</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1776,21 +1777,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1803,10 +1804,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>454160</v>
+        <v>454172</v>
       </c>
       <c r="R12" t="n">
-        <v>7169971</v>
+        <v>7170015</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1843,7 +1844,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På högstubbe av björk.</t>
+          <t>På grangrenar.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1871,10 +1872,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120046842</v>
+        <v>120046420</v>
       </c>
       <c r="B13" t="n">
-        <v>94251</v>
+        <v>78526</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1883,31 +1884,30 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>756</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Käppkrokmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hamatocaulis vernicosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Mitt.) Hedenäs</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1915,10 +1915,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>454168</v>
+        <v>454365</v>
       </c>
       <c r="R13" t="n">
-        <v>7170020</v>
+        <v>7169956</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1951,6 +1951,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-08-18</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På gammal björk.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1978,10 +1983,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120046668</v>
+        <v>120046880</v>
       </c>
       <c r="B14" t="n">
-        <v>79608</v>
+        <v>97928</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1990,30 +1995,31 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2081</v>
+        <v>221952</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2021,10 +2027,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>454160</v>
+        <v>454180</v>
       </c>
       <c r="R14" t="n">
-        <v>7169971</v>
+        <v>7170065</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2057,11 +2063,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-08-18</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2196,10 +2197,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120046632</v>
+        <v>120046842</v>
       </c>
       <c r="B16" t="n">
-        <v>97824</v>
+        <v>94251</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2212,21 +2213,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219790</v>
+        <v>756</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Käppkrokmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Hamatocaulis vernicosus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Mitt.) Hedenäs</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2240,10 +2241,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>454185</v>
+        <v>454168</v>
       </c>
       <c r="R16" t="n">
-        <v>7169988</v>
+        <v>7170020</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2303,10 +2304,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120046720</v>
+        <v>120046587</v>
       </c>
       <c r="B17" t="n">
-        <v>90558</v>
+        <v>91494</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2315,25 +2316,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1108</v>
+        <v>4769</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2346,10 +2347,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>454158</v>
+        <v>454254</v>
       </c>
       <c r="R17" t="n">
-        <v>7169997</v>
+        <v>7169982</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2382,11 +2383,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-08-18</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På torrgran.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2414,10 +2410,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120046554</v>
+        <v>120046668</v>
       </c>
       <c r="B18" t="n">
-        <v>79636</v>
+        <v>79608</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2426,25 +2422,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2457,10 +2453,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>454274</v>
+        <v>454160</v>
       </c>
       <c r="R18" t="n">
-        <v>7170002</v>
+        <v>7169971</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2497,7 +2493,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På klen rönn.</t>
+          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2525,10 +2521,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120046845</v>
+        <v>120046580</v>
       </c>
       <c r="B19" t="n">
-        <v>93743</v>
+        <v>97928</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2541,21 +2537,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2412</v>
+        <v>221952</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Källmossa</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Philonotis fontana</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2569,10 +2565,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>454168</v>
+        <v>454254</v>
       </c>
       <c r="R19" t="n">
-        <v>7170020</v>
+        <v>7169982</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2632,10 +2628,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120046702</v>
+        <v>120046869</v>
       </c>
       <c r="B20" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2644,30 +2640,31 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2675,10 +2672,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>454157</v>
+        <v>454180</v>
       </c>
       <c r="R20" t="n">
-        <v>7169992</v>
+        <v>7170065</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2711,11 +2708,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-08-18</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>På grangrenar.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2743,10 +2735,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120046420</v>
+        <v>120046632</v>
       </c>
       <c r="B21" t="n">
-        <v>78526</v>
+        <v>97824</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2755,30 +2747,31 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2786,10 +2779,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>454365</v>
+        <v>454185</v>
       </c>
       <c r="R21" t="n">
-        <v>7169956</v>
+        <v>7169988</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2822,11 +2815,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-08-18</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>På gammal björk.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2854,10 +2842,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120046948</v>
+        <v>120046472</v>
       </c>
       <c r="B22" t="n">
-        <v>97930</v>
+        <v>97928</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2870,21 +2858,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219847</v>
+        <v>221952</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2898,10 +2886,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>454190</v>
+        <v>454355</v>
       </c>
       <c r="R22" t="n">
-        <v>7170110</v>
+        <v>7169944</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2961,10 +2949,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120046472</v>
+        <v>120046564</v>
       </c>
       <c r="B23" t="n">
-        <v>97928</v>
+        <v>91547</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2977,27 +2965,26 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221952</v>
+        <v>5836</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Guldkremla</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Russula aurea</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Pers.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3005,10 +2992,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>454355</v>
+        <v>454274</v>
       </c>
       <c r="R23" t="n">
-        <v>7169944</v>
+        <v>7170002</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3068,10 +3055,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120046765</v>
+        <v>120046671</v>
       </c>
       <c r="B24" t="n">
-        <v>90580</v>
+        <v>79636</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3080,25 +3067,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3111,10 +3098,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>454176</v>
+        <v>454160</v>
       </c>
       <c r="R24" t="n">
-        <v>7170001</v>
+        <v>7169971</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3151,7 +3138,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På granlåga.</t>
+          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3179,10 +3166,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120046587</v>
+        <v>120046702</v>
       </c>
       <c r="B25" t="n">
-        <v>91494</v>
+        <v>78526</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3191,25 +3178,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4769</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3222,10 +3209,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>454254</v>
+        <v>454157</v>
       </c>
       <c r="R25" t="n">
-        <v>7169982</v>
+        <v>7169992</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3258,6 +3245,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-08-18</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>På grangrenar.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3285,10 +3277,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120046421</v>
+        <v>120046720</v>
       </c>
       <c r="B26" t="n">
-        <v>98242</v>
+        <v>90558</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3297,31 +3289,30 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>219880</v>
+        <v>1108</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3329,10 +3320,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>454365</v>
+        <v>454158</v>
       </c>
       <c r="R26" t="n">
-        <v>7169956</v>
+        <v>7169997</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3365,6 +3356,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-08-18</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>På torrgran.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3392,10 +3388,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120046876</v>
+        <v>120046765</v>
       </c>
       <c r="B27" t="n">
-        <v>97806</v>
+        <v>90580</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3404,31 +3400,30 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>219795</v>
+        <v>5432</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3436,10 +3431,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>454180</v>
+        <v>454176</v>
       </c>
       <c r="R27" t="n">
-        <v>7170065</v>
+        <v>7170001</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3472,6 +3467,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-08-18</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>På granlåga.</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 47636-2022 artfynd.xlsx
+++ b/artfynd/A 47636-2022 artfynd.xlsx
@@ -1325,10 +1325,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120046528</v>
+        <v>120046602</v>
       </c>
       <c r="B8" t="n">
-        <v>97806</v>
+        <v>90527</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1341,27 +1341,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219795</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1369,10 +1368,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>454297</v>
+        <v>454188</v>
       </c>
       <c r="R8" t="n">
-        <v>7169982</v>
+        <v>7169986</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1405,6 +1404,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-08-18</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På granhögstubbe.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1432,10 +1436,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120046602</v>
+        <v>120046528</v>
       </c>
       <c r="B9" t="n">
-        <v>90527</v>
+        <v>97806</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1448,26 +1452,27 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>219795</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1475,10 +1480,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>454188</v>
+        <v>454297</v>
       </c>
       <c r="R9" t="n">
-        <v>7169986</v>
+        <v>7169982</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1511,11 +1516,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-08-18</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På granhögstubbe.</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 47636-2022 artfynd.xlsx
+++ b/artfynd/A 47636-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120046676</v>
+        <v>120046528</v>
       </c>
       <c r="B2" t="n">
-        <v>74643</v>
+        <v>97806</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1467</v>
+        <v>219795</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>454160</v>
+        <v>454297</v>
       </c>
       <c r="R2" t="n">
-        <v>7169971</v>
+        <v>7169982</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -754,11 +755,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-08-18</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På högstubbe av björk.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120046948</v>
+        <v>120046580</v>
       </c>
       <c r="B3" t="n">
-        <v>97930</v>
+        <v>97928</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219847</v>
+        <v>221952</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -830,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>454190</v>
+        <v>454254</v>
       </c>
       <c r="R3" t="n">
-        <v>7170110</v>
+        <v>7169982</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -893,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120046845</v>
+        <v>120046486</v>
       </c>
       <c r="B4" t="n">
-        <v>93743</v>
+        <v>94311</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2412</v>
+        <v>2809</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Källmossa</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Philonotis fontana</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -937,10 +933,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>454168</v>
+        <v>454316</v>
       </c>
       <c r="R4" t="n">
-        <v>7170020</v>
+        <v>7169955</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1107,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120046446</v>
+        <v>120046676</v>
       </c>
       <c r="B6" t="n">
-        <v>78526</v>
+        <v>74643</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,21 +1119,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1150,10 +1146,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454357</v>
+        <v>454160</v>
       </c>
       <c r="R6" t="n">
-        <v>7169950</v>
+        <v>7169971</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1190,7 +1186,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På grangrenar.</t>
+          <t>På högstubbe av björk.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1218,10 +1214,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120046421</v>
+        <v>120046564</v>
       </c>
       <c r="B7" t="n">
-        <v>98242</v>
+        <v>91547</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1234,27 +1230,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219880</v>
+        <v>5836</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Guldkremla</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Russula aurea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>Pers.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1262,10 +1257,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>454365</v>
+        <v>454274</v>
       </c>
       <c r="R7" t="n">
-        <v>7169956</v>
+        <v>7170002</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1325,10 +1320,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120046602</v>
+        <v>120046446</v>
       </c>
       <c r="B8" t="n">
-        <v>90527</v>
+        <v>78526</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1337,25 +1332,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1368,10 +1363,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>454188</v>
+        <v>454357</v>
       </c>
       <c r="R8" t="n">
-        <v>7169986</v>
+        <v>7169950</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1408,7 +1403,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På granhögstubbe.</t>
+          <t>På grangrenar.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1436,10 +1431,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120046528</v>
+        <v>120046587</v>
       </c>
       <c r="B9" t="n">
-        <v>97806</v>
+        <v>91494</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1452,27 +1447,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219795</v>
+        <v>4769</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1480,7 +1474,7 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>454297</v>
+        <v>454254</v>
       </c>
       <c r="R9" t="n">
         <v>7169982</v>
@@ -1543,10 +1537,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120046554</v>
+        <v>120046602</v>
       </c>
       <c r="B10" t="n">
-        <v>79636</v>
+        <v>90527</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1559,21 +1553,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1586,10 +1580,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>454274</v>
+        <v>454188</v>
       </c>
       <c r="R10" t="n">
-        <v>7170002</v>
+        <v>7169986</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1626,7 +1620,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På klen rönn.</t>
+          <t>På granhögstubbe.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1654,10 +1648,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120046626</v>
+        <v>120046554</v>
       </c>
       <c r="B11" t="n">
-        <v>104994</v>
+        <v>79636</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1670,27 +1664,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221725</v>
+        <v>6462</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1698,10 +1691,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>454185</v>
+        <v>454274</v>
       </c>
       <c r="R11" t="n">
-        <v>7169988</v>
+        <v>7170002</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1734,6 +1727,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-08-18</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På klen rönn.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1761,10 +1759,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120046814</v>
+        <v>120046869</v>
       </c>
       <c r="B12" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1773,30 +1771,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1804,10 +1803,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>454172</v>
+        <v>454180</v>
       </c>
       <c r="R12" t="n">
-        <v>7170015</v>
+        <v>7170065</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1840,11 +1839,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-08-18</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>På grangrenar.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1872,10 +1866,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120046420</v>
+        <v>120046632</v>
       </c>
       <c r="B13" t="n">
-        <v>78526</v>
+        <v>97824</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1884,30 +1878,31 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1915,10 +1910,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>454365</v>
+        <v>454185</v>
       </c>
       <c r="R13" t="n">
-        <v>7169956</v>
+        <v>7169988</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1951,11 +1946,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-08-18</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>På gammal björk.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1983,10 +1973,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120046880</v>
+        <v>120046671</v>
       </c>
       <c r="B14" t="n">
-        <v>97928</v>
+        <v>79636</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1999,27 +1989,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221952</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2027,10 +2016,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>454180</v>
+        <v>454160</v>
       </c>
       <c r="R14" t="n">
-        <v>7170065</v>
+        <v>7169971</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2063,6 +2052,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-08-18</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2090,10 +2084,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120046486</v>
+        <v>120046814</v>
       </c>
       <c r="B15" t="n">
-        <v>94311</v>
+        <v>78526</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2102,31 +2096,30 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2809</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2134,10 +2127,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>454316</v>
+        <v>454172</v>
       </c>
       <c r="R15" t="n">
-        <v>7169955</v>
+        <v>7170015</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2170,6 +2163,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-08-18</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På grangrenar.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2197,10 +2195,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120046842</v>
+        <v>120046720</v>
       </c>
       <c r="B16" t="n">
-        <v>94251</v>
+        <v>90558</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2209,31 +2207,30 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>756</v>
+        <v>1108</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Käppkrokmossa</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hamatocaulis vernicosus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Mitt.) Hedenäs</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2241,10 +2238,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>454168</v>
+        <v>454158</v>
       </c>
       <c r="R16" t="n">
-        <v>7170020</v>
+        <v>7169997</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2277,6 +2274,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-08-18</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På torrgran.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2304,10 +2306,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120046587</v>
+        <v>120046880</v>
       </c>
       <c r="B17" t="n">
-        <v>91494</v>
+        <v>97928</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2320,26 +2322,27 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4769</v>
+        <v>221952</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2347,10 +2350,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>454254</v>
+        <v>454180</v>
       </c>
       <c r="R17" t="n">
-        <v>7169982</v>
+        <v>7170065</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2521,10 +2524,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120046580</v>
+        <v>120046948</v>
       </c>
       <c r="B19" t="n">
-        <v>97928</v>
+        <v>97930</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2537,21 +2540,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221952</v>
+        <v>219847</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2565,10 +2568,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>454254</v>
+        <v>454190</v>
       </c>
       <c r="R19" t="n">
-        <v>7169982</v>
+        <v>7170110</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2628,10 +2631,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120046869</v>
+        <v>120046626</v>
       </c>
       <c r="B20" t="n">
-        <v>97907</v>
+        <v>104994</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2640,25 +2643,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2672,10 +2675,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>454180</v>
+        <v>454185</v>
       </c>
       <c r="R20" t="n">
-        <v>7170065</v>
+        <v>7169988</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2735,10 +2738,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120046632</v>
+        <v>120046472</v>
       </c>
       <c r="B21" t="n">
-        <v>97824</v>
+        <v>97928</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2751,21 +2754,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219790</v>
+        <v>221952</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2779,10 +2782,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>454185</v>
+        <v>454355</v>
       </c>
       <c r="R21" t="n">
-        <v>7169988</v>
+        <v>7169944</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2842,10 +2845,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120046472</v>
+        <v>120046845</v>
       </c>
       <c r="B22" t="n">
-        <v>97928</v>
+        <v>93743</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2858,21 +2861,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221952</v>
+        <v>2412</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Källmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Philonotis fontana</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2886,10 +2889,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>454355</v>
+        <v>454168</v>
       </c>
       <c r="R22" t="n">
-        <v>7169944</v>
+        <v>7170020</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2949,10 +2952,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120046564</v>
+        <v>120046842</v>
       </c>
       <c r="B23" t="n">
-        <v>91547</v>
+        <v>94251</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2965,26 +2968,27 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5836</v>
+        <v>756</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Guldkremla</t>
+          <t>Käppkrokmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Russula aurea</t>
+          <t>Hamatocaulis vernicosus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Pers.</t>
+          <t>(Mitt.) Hedenäs</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2992,10 +2996,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>454274</v>
+        <v>454168</v>
       </c>
       <c r="R23" t="n">
-        <v>7170002</v>
+        <v>7170020</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3055,10 +3059,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120046671</v>
+        <v>120046702</v>
       </c>
       <c r="B24" t="n">
-        <v>79636</v>
+        <v>78526</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3067,25 +3071,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3098,10 +3102,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>454160</v>
+        <v>454157</v>
       </c>
       <c r="R24" t="n">
-        <v>7169971</v>
+        <v>7169992</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3138,7 +3142,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På rönn.</t>
+          <t>På grangrenar.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3166,10 +3170,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120046702</v>
+        <v>120046765</v>
       </c>
       <c r="B25" t="n">
-        <v>78526</v>
+        <v>90580</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3182,21 +3186,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3209,10 +3213,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>454157</v>
+        <v>454176</v>
       </c>
       <c r="R25" t="n">
-        <v>7169992</v>
+        <v>7170001</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3249,7 +3253,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På grangrenar.</t>
+          <t>På granlåga.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3277,10 +3281,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120046720</v>
+        <v>120046420</v>
       </c>
       <c r="B26" t="n">
-        <v>90558</v>
+        <v>78526</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3293,21 +3297,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3320,10 +3324,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>454158</v>
+        <v>454365</v>
       </c>
       <c r="R26" t="n">
-        <v>7169997</v>
+        <v>7169956</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3360,7 +3364,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På torrgran.</t>
+          <t>På gammal björk.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3388,10 +3392,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120046765</v>
+        <v>120046421</v>
       </c>
       <c r="B27" t="n">
-        <v>90580</v>
+        <v>98242</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3400,30 +3404,31 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>219880</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3431,10 +3436,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>454176</v>
+        <v>454365</v>
       </c>
       <c r="R27" t="n">
-        <v>7170001</v>
+        <v>7169956</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3467,11 +3472,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-08-18</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>På granlåga.</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 47636-2022 artfynd.xlsx
+++ b/artfynd/A 47636-2022 artfynd.xlsx
@@ -2631,10 +2631,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120046626</v>
+        <v>120046472</v>
       </c>
       <c r="B20" t="n">
-        <v>104994</v>
+        <v>97928</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2647,21 +2647,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221725</v>
+        <v>221952</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2675,10 +2675,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>454185</v>
+        <v>454355</v>
       </c>
       <c r="R20" t="n">
-        <v>7169988</v>
+        <v>7169944</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2738,10 +2738,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120046472</v>
+        <v>120046626</v>
       </c>
       <c r="B21" t="n">
-        <v>97928</v>
+        <v>104994</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2754,21 +2754,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221952</v>
+        <v>221725</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2782,10 +2782,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>454355</v>
+        <v>454185</v>
       </c>
       <c r="R21" t="n">
-        <v>7169944</v>
+        <v>7169988</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>

--- a/artfynd/A 47636-2022 artfynd.xlsx
+++ b/artfynd/A 47636-2022 artfynd.xlsx
@@ -2631,10 +2631,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120046472</v>
+        <v>120046626</v>
       </c>
       <c r="B20" t="n">
-        <v>97928</v>
+        <v>104994</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2647,21 +2647,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221952</v>
+        <v>221725</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2675,10 +2675,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>454355</v>
+        <v>454185</v>
       </c>
       <c r="R20" t="n">
-        <v>7169944</v>
+        <v>7169988</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2738,10 +2738,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120046626</v>
+        <v>120046472</v>
       </c>
       <c r="B21" t="n">
-        <v>104994</v>
+        <v>97928</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2754,21 +2754,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221725</v>
+        <v>221952</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2782,10 +2782,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>454185</v>
+        <v>454355</v>
       </c>
       <c r="R21" t="n">
-        <v>7169988</v>
+        <v>7169944</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>

--- a/artfynd/A 47636-2022 artfynd.xlsx
+++ b/artfynd/A 47636-2022 artfynd.xlsx
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120046486</v>
+        <v>120046876</v>
       </c>
       <c r="B4" t="n">
-        <v>94311</v>
+        <v>97806</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2809</v>
+        <v>219795</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -933,10 +933,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>454316</v>
+        <v>454180</v>
       </c>
       <c r="R4" t="n">
-        <v>7169955</v>
+        <v>7170065</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120046876</v>
+        <v>120046486</v>
       </c>
       <c r="B5" t="n">
-        <v>97806</v>
+        <v>94311</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,21 +1012,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219795</v>
+        <v>2809</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>454180</v>
+        <v>454316</v>
       </c>
       <c r="R5" t="n">
-        <v>7170065</v>
+        <v>7169955</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1866,10 +1866,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120046632</v>
+        <v>120046671</v>
       </c>
       <c r="B13" t="n">
-        <v>97824</v>
+        <v>79636</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1882,27 +1882,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219790</v>
+        <v>6462</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1910,10 +1909,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>454185</v>
+        <v>454160</v>
       </c>
       <c r="R13" t="n">
-        <v>7169988</v>
+        <v>7169971</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1946,6 +1945,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-08-18</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1973,10 +1977,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120046671</v>
+        <v>120046632</v>
       </c>
       <c r="B14" t="n">
-        <v>79636</v>
+        <v>97824</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1989,26 +1993,27 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6462</v>
+        <v>219790</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2016,10 +2021,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>454160</v>
+        <v>454185</v>
       </c>
       <c r="R14" t="n">
-        <v>7169971</v>
+        <v>7169988</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2052,11 +2057,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-08-18</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 47636-2022 artfynd.xlsx
+++ b/artfynd/A 47636-2022 artfynd.xlsx
@@ -1866,10 +1866,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120046671</v>
+        <v>120046632</v>
       </c>
       <c r="B13" t="n">
-        <v>79636</v>
+        <v>97824</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1882,26 +1882,27 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6462</v>
+        <v>219790</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1909,10 +1910,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>454160</v>
+        <v>454185</v>
       </c>
       <c r="R13" t="n">
-        <v>7169971</v>
+        <v>7169988</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1945,11 +1946,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-08-18</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1977,10 +1973,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120046632</v>
+        <v>120046671</v>
       </c>
       <c r="B14" t="n">
-        <v>97824</v>
+        <v>79636</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1993,27 +1989,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219790</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2021,10 +2016,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>454185</v>
+        <v>454160</v>
       </c>
       <c r="R14" t="n">
-        <v>7169988</v>
+        <v>7169971</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2057,6 +2052,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-08-18</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2631,10 +2631,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120046626</v>
+        <v>120046472</v>
       </c>
       <c r="B20" t="n">
-        <v>104994</v>
+        <v>97928</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2647,21 +2647,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221725</v>
+        <v>221952</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2675,10 +2675,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>454185</v>
+        <v>454355</v>
       </c>
       <c r="R20" t="n">
-        <v>7169988</v>
+        <v>7169944</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2738,10 +2738,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120046472</v>
+        <v>120046626</v>
       </c>
       <c r="B21" t="n">
-        <v>97928</v>
+        <v>104994</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2754,21 +2754,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221952</v>
+        <v>221725</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2782,10 +2782,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>454355</v>
+        <v>454185</v>
       </c>
       <c r="R21" t="n">
-        <v>7169944</v>
+        <v>7169988</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>

--- a/artfynd/A 47636-2022 artfynd.xlsx
+++ b/artfynd/A 47636-2022 artfynd.xlsx
@@ -1866,10 +1866,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120046632</v>
+        <v>120046671</v>
       </c>
       <c r="B13" t="n">
-        <v>97824</v>
+        <v>79636</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1882,27 +1882,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219790</v>
+        <v>6462</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1910,10 +1909,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>454185</v>
+        <v>454160</v>
       </c>
       <c r="R13" t="n">
-        <v>7169988</v>
+        <v>7169971</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1946,6 +1945,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-08-18</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1973,10 +1977,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120046671</v>
+        <v>120046632</v>
       </c>
       <c r="B14" t="n">
-        <v>79636</v>
+        <v>97824</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1989,26 +1993,27 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6462</v>
+        <v>219790</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2016,10 +2021,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>454160</v>
+        <v>454185</v>
       </c>
       <c r="R14" t="n">
-        <v>7169971</v>
+        <v>7169988</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2052,11 +2057,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-08-18</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2631,10 +2631,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120046472</v>
+        <v>120046626</v>
       </c>
       <c r="B20" t="n">
-        <v>97928</v>
+        <v>104994</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2647,21 +2647,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221952</v>
+        <v>221725</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2675,10 +2675,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>454355</v>
+        <v>454185</v>
       </c>
       <c r="R20" t="n">
-        <v>7169944</v>
+        <v>7169988</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2738,10 +2738,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120046626</v>
+        <v>120046472</v>
       </c>
       <c r="B21" t="n">
-        <v>104994</v>
+        <v>97928</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2754,21 +2754,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221725</v>
+        <v>221952</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2782,10 +2782,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>454185</v>
+        <v>454355</v>
       </c>
       <c r="R21" t="n">
-        <v>7169988</v>
+        <v>7169944</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>

--- a/artfynd/A 47636-2022 artfynd.xlsx
+++ b/artfynd/A 47636-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120046528</v>
+        <v>120046472</v>
       </c>
       <c r="B2" t="n">
-        <v>97806</v>
+        <v>97951</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219795</v>
+        <v>221952</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>454297</v>
+        <v>454355</v>
       </c>
       <c r="R2" t="n">
-        <v>7169982</v>
+        <v>7169944</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -785,7 +785,7 @@
         <v>120046580</v>
       </c>
       <c r="B3" t="n">
-        <v>97928</v>
+        <v>97951</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120046876</v>
+        <v>120046668</v>
       </c>
       <c r="B4" t="n">
-        <v>97806</v>
+        <v>79624</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,31 +901,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219795</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -933,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>454180</v>
+        <v>454160</v>
       </c>
       <c r="R4" t="n">
-        <v>7170065</v>
+        <v>7169971</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -969,6 +968,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-08-18</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +1000,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120046486</v>
+        <v>120046765</v>
       </c>
       <c r="B5" t="n">
-        <v>94311</v>
+        <v>90598</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1008,31 +1012,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2809</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1040,10 +1043,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>454316</v>
+        <v>454176</v>
       </c>
       <c r="R5" t="n">
-        <v>7169955</v>
+        <v>7170001</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1076,6 +1079,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-08-18</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På granlåga.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1106,7 +1114,7 @@
         <v>120046676</v>
       </c>
       <c r="B6" t="n">
-        <v>74643</v>
+        <v>74659</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1214,10 +1222,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120046564</v>
+        <v>120046421</v>
       </c>
       <c r="B7" t="n">
-        <v>91547</v>
+        <v>98265</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1230,26 +1238,27 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5836</v>
+        <v>219880</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Guldkremla</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Russula aurea</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Pers.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1257,10 +1266,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>454274</v>
+        <v>454365</v>
       </c>
       <c r="R7" t="n">
-        <v>7170002</v>
+        <v>7169956</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1320,10 +1329,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120046446</v>
+        <v>120046632</v>
       </c>
       <c r="B8" t="n">
-        <v>78526</v>
+        <v>97847</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1332,30 +1341,31 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1363,10 +1373,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>454357</v>
+        <v>454185</v>
       </c>
       <c r="R8" t="n">
-        <v>7169950</v>
+        <v>7169988</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1399,11 +1409,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-08-18</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På grangrenar.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1431,10 +1436,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120046587</v>
+        <v>120046876</v>
       </c>
       <c r="B9" t="n">
-        <v>91494</v>
+        <v>97829</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1447,26 +1452,27 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4769</v>
+        <v>219795</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1474,10 +1480,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>454254</v>
+        <v>454180</v>
       </c>
       <c r="R9" t="n">
-        <v>7169982</v>
+        <v>7170065</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1537,10 +1543,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120046602</v>
+        <v>120046554</v>
       </c>
       <c r="B10" t="n">
-        <v>90527</v>
+        <v>79652</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1553,21 +1559,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1580,10 +1586,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>454188</v>
+        <v>454274</v>
       </c>
       <c r="R10" t="n">
-        <v>7169986</v>
+        <v>7170002</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1620,7 +1626,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På granhögstubbe.</t>
+          <t>På klen rönn.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1648,10 +1654,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120046554</v>
+        <v>120046486</v>
       </c>
       <c r="B11" t="n">
-        <v>79636</v>
+        <v>94334</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1664,26 +1670,27 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6462</v>
+        <v>2809</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1691,10 +1698,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>454274</v>
+        <v>454316</v>
       </c>
       <c r="R11" t="n">
-        <v>7170002</v>
+        <v>7169955</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1727,11 +1734,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-08-18</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>På klen rönn.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1759,10 +1761,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120046869</v>
+        <v>120046948</v>
       </c>
       <c r="B12" t="n">
-        <v>97907</v>
+        <v>97953</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1771,25 +1773,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>219847</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1803,10 +1805,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>454180</v>
+        <v>454190</v>
       </c>
       <c r="R12" t="n">
-        <v>7170065</v>
+        <v>7170110</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1866,10 +1868,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120046671</v>
+        <v>120046602</v>
       </c>
       <c r="B13" t="n">
-        <v>79636</v>
+        <v>90545</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1882,21 +1884,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6462</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1909,10 +1911,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>454160</v>
+        <v>454188</v>
       </c>
       <c r="R13" t="n">
-        <v>7169971</v>
+        <v>7169986</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1949,7 +1951,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På rönn.</t>
+          <t>På granhögstubbe.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1977,10 +1979,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120046632</v>
+        <v>120046587</v>
       </c>
       <c r="B14" t="n">
-        <v>97824</v>
+        <v>91512</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1993,27 +1995,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219790</v>
+        <v>4769</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2021,10 +2022,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>454185</v>
+        <v>454254</v>
       </c>
       <c r="R14" t="n">
-        <v>7169988</v>
+        <v>7169982</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2084,10 +2085,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120046814</v>
+        <v>120046564</v>
       </c>
       <c r="B15" t="n">
-        <v>78526</v>
+        <v>91565</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2096,25 +2097,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>5836</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Guldkremla</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Russula aurea</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pers.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2127,10 +2128,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>454172</v>
+        <v>454274</v>
       </c>
       <c r="R15" t="n">
-        <v>7170015</v>
+        <v>7170002</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2163,11 +2164,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-08-18</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På grangrenar.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2195,10 +2191,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120046720</v>
+        <v>120046420</v>
       </c>
       <c r="B16" t="n">
-        <v>90558</v>
+        <v>78542</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2211,21 +2207,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2238,10 +2234,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>454158</v>
+        <v>454365</v>
       </c>
       <c r="R16" t="n">
-        <v>7169997</v>
+        <v>7169956</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2278,7 +2274,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På torrgran.</t>
+          <t>På gammal björk.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2306,10 +2302,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120046880</v>
+        <v>120046671</v>
       </c>
       <c r="B17" t="n">
-        <v>97928</v>
+        <v>79652</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2322,27 +2318,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221952</v>
+        <v>6462</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2350,10 +2345,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>454180</v>
+        <v>454160</v>
       </c>
       <c r="R17" t="n">
-        <v>7170065</v>
+        <v>7169971</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2386,6 +2381,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-08-18</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2413,10 +2413,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120046668</v>
+        <v>120046842</v>
       </c>
       <c r="B18" t="n">
-        <v>79608</v>
+        <v>94274</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2425,30 +2425,31 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2081</v>
+        <v>756</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Käppkrokmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hamatocaulis vernicosus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Mitt.) Hedenäs</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2456,10 +2457,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>454160</v>
+        <v>454168</v>
       </c>
       <c r="R18" t="n">
-        <v>7169971</v>
+        <v>7170020</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2492,11 +2493,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-08-18</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2524,10 +2520,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120046948</v>
+        <v>120046528</v>
       </c>
       <c r="B19" t="n">
-        <v>97930</v>
+        <v>97829</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2540,21 +2536,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219847</v>
+        <v>219795</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2568,10 +2564,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>454190</v>
+        <v>454297</v>
       </c>
       <c r="R19" t="n">
-        <v>7170110</v>
+        <v>7169982</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2631,10 +2627,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120046626</v>
+        <v>120046880</v>
       </c>
       <c r="B20" t="n">
-        <v>104994</v>
+        <v>97951</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2647,21 +2643,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221725</v>
+        <v>221952</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2675,10 +2671,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>454185</v>
+        <v>454180</v>
       </c>
       <c r="R20" t="n">
-        <v>7169988</v>
+        <v>7170065</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2738,10 +2734,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120046472</v>
+        <v>120046869</v>
       </c>
       <c r="B21" t="n">
-        <v>97928</v>
+        <v>97930</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2750,25 +2746,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2782,10 +2778,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>454355</v>
+        <v>454180</v>
       </c>
       <c r="R21" t="n">
-        <v>7169944</v>
+        <v>7170065</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2848,7 +2844,7 @@
         <v>120046845</v>
       </c>
       <c r="B22" t="n">
-        <v>93743</v>
+        <v>93766</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2952,10 +2948,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120046842</v>
+        <v>120046720</v>
       </c>
       <c r="B23" t="n">
-        <v>94251</v>
+        <v>90576</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2964,31 +2960,30 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>756</v>
+        <v>1108</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Käppkrokmossa</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hamatocaulis vernicosus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Mitt.) Hedenäs</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2996,10 +2991,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>454168</v>
+        <v>454158</v>
       </c>
       <c r="R23" t="n">
-        <v>7170020</v>
+        <v>7169997</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3032,6 +3027,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-08-18</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>På torrgran.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3059,10 +3059,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120046702</v>
+        <v>120046814</v>
       </c>
       <c r="B24" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3102,10 +3102,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>454157</v>
+        <v>454172</v>
       </c>
       <c r="R24" t="n">
-        <v>7169992</v>
+        <v>7170015</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3170,10 +3170,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120046765</v>
+        <v>120046626</v>
       </c>
       <c r="B25" t="n">
-        <v>90580</v>
+        <v>105017</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3182,30 +3182,31 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>221725</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3213,10 +3214,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>454176</v>
+        <v>454185</v>
       </c>
       <c r="R25" t="n">
-        <v>7170001</v>
+        <v>7169988</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3249,11 +3250,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-08-18</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>På granlåga.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3281,10 +3277,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120046420</v>
+        <v>120046446</v>
       </c>
       <c r="B26" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3324,10 +3320,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>454365</v>
+        <v>454357</v>
       </c>
       <c r="R26" t="n">
-        <v>7169956</v>
+        <v>7169950</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3364,7 +3360,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På gammal björk.</t>
+          <t>På grangrenar.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3392,10 +3388,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120046421</v>
+        <v>120046702</v>
       </c>
       <c r="B27" t="n">
-        <v>98242</v>
+        <v>78542</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3404,31 +3400,30 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>219880</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3436,10 +3431,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>454365</v>
+        <v>454157</v>
       </c>
       <c r="R27" t="n">
-        <v>7169956</v>
+        <v>7169992</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3472,6 +3467,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-08-18</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>På grangrenar.</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 47636-2022 artfynd.xlsx
+++ b/artfynd/A 47636-2022 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120046580</v>
+        <v>120046668</v>
       </c>
       <c r="B3" t="n">
-        <v>97951</v>
+        <v>79624</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,31 +794,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221952</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -826,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>454254</v>
+        <v>454160</v>
       </c>
       <c r="R3" t="n">
-        <v>7169982</v>
+        <v>7169971</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -862,6 +861,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-08-18</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120046668</v>
+        <v>120046580</v>
       </c>
       <c r="B4" t="n">
-        <v>79624</v>
+        <v>97951</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,30 +905,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>221952</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -932,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>454160</v>
+        <v>454254</v>
       </c>
       <c r="R4" t="n">
-        <v>7169971</v>
+        <v>7169982</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -968,11 +973,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-08-18</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1436,10 +1436,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120046876</v>
+        <v>120046486</v>
       </c>
       <c r="B9" t="n">
-        <v>97829</v>
+        <v>94334</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1452,21 +1452,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219795</v>
+        <v>2809</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1480,10 +1480,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>454180</v>
+        <v>454316</v>
       </c>
       <c r="R9" t="n">
-        <v>7170065</v>
+        <v>7169955</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1654,10 +1654,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120046486</v>
+        <v>120046876</v>
       </c>
       <c r="B11" t="n">
-        <v>94334</v>
+        <v>97829</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1670,21 +1670,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2809</v>
+        <v>219795</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1698,10 +1698,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>454316</v>
+        <v>454180</v>
       </c>
       <c r="R11" t="n">
-        <v>7169955</v>
+        <v>7170065</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -2085,10 +2085,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120046564</v>
+        <v>120046420</v>
       </c>
       <c r="B15" t="n">
-        <v>91565</v>
+        <v>78542</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2097,25 +2097,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5836</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Guldkremla</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Russula aurea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Pers.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2128,10 +2128,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>454274</v>
+        <v>454365</v>
       </c>
       <c r="R15" t="n">
-        <v>7170002</v>
+        <v>7169956</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2164,6 +2164,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-08-18</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På gammal björk.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2191,10 +2196,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120046420</v>
+        <v>120046671</v>
       </c>
       <c r="B16" t="n">
-        <v>78542</v>
+        <v>79652</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2203,25 +2208,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2234,10 +2239,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>454365</v>
+        <v>454160</v>
       </c>
       <c r="R16" t="n">
-        <v>7169956</v>
+        <v>7169971</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2274,7 +2279,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På gammal björk.</t>
+          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2302,10 +2307,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120046671</v>
+        <v>120046564</v>
       </c>
       <c r="B17" t="n">
-        <v>79652</v>
+        <v>91565</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2318,21 +2323,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6462</v>
+        <v>5836</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Guldkremla</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Russula aurea</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Pers.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2345,10 +2350,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>454160</v>
+        <v>454274</v>
       </c>
       <c r="R17" t="n">
-        <v>7169971</v>
+        <v>7170002</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2381,11 +2386,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-08-18</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 47636-2022 artfynd.xlsx
+++ b/artfynd/A 47636-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120046472</v>
+        <v>120046420</v>
       </c>
       <c r="B2" t="n">
-        <v>97951</v>
+        <v>78542</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>454355</v>
+        <v>454365</v>
       </c>
       <c r="R2" t="n">
-        <v>7169944</v>
+        <v>7169956</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -755,6 +754,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-08-18</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På gammal björk.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120046668</v>
+        <v>120046876</v>
       </c>
       <c r="B3" t="n">
-        <v>79624</v>
+        <v>97829</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,30 +798,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>219795</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -825,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>454160</v>
+        <v>454180</v>
       </c>
       <c r="R3" t="n">
-        <v>7169971</v>
+        <v>7170065</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -861,11 +866,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-08-18</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,10 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120046580</v>
+        <v>120046765</v>
       </c>
       <c r="B4" t="n">
-        <v>97951</v>
+        <v>90598</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,31 +905,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221952</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -937,10 +936,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>454254</v>
+        <v>454176</v>
       </c>
       <c r="R4" t="n">
-        <v>7169982</v>
+        <v>7170001</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -973,6 +972,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-08-18</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På granlåga.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1000,10 +1004,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120046765</v>
+        <v>120046528</v>
       </c>
       <c r="B5" t="n">
-        <v>90598</v>
+        <v>97829</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,30 +1016,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>219795</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1043,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>454176</v>
+        <v>454297</v>
       </c>
       <c r="R5" t="n">
-        <v>7170001</v>
+        <v>7169982</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1079,11 +1084,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-08-18</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På granlåga.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,10 +1111,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120046676</v>
+        <v>120046948</v>
       </c>
       <c r="B6" t="n">
-        <v>74659</v>
+        <v>97953</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,30 +1123,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1467</v>
+        <v>219847</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1154,10 +1155,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454160</v>
+        <v>454190</v>
       </c>
       <c r="R6" t="n">
-        <v>7169971</v>
+        <v>7170110</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1190,11 +1191,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-08-18</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På högstubbe av björk.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1222,10 +1218,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120046421</v>
+        <v>120046842</v>
       </c>
       <c r="B7" t="n">
-        <v>98265</v>
+        <v>94274</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1238,21 +1234,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219880</v>
+        <v>756</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Käppkrokmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Hamatocaulis vernicosus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Mitt.) Hedenäs</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1266,10 +1262,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>454365</v>
+        <v>454168</v>
       </c>
       <c r="R7" t="n">
-        <v>7169956</v>
+        <v>7170020</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1329,10 +1325,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120046632</v>
+        <v>120046671</v>
       </c>
       <c r="B8" t="n">
-        <v>97847</v>
+        <v>79652</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1345,27 +1341,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219790</v>
+        <v>6462</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1373,10 +1368,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>454185</v>
+        <v>454160</v>
       </c>
       <c r="R8" t="n">
-        <v>7169988</v>
+        <v>7169971</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1409,6 +1404,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-08-18</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1436,10 +1436,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120046486</v>
+        <v>120046720</v>
       </c>
       <c r="B9" t="n">
-        <v>94334</v>
+        <v>90576</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1448,31 +1448,30 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2809</v>
+        <v>1108</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1480,10 +1479,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>454316</v>
+        <v>454158</v>
       </c>
       <c r="R9" t="n">
-        <v>7169955</v>
+        <v>7169997</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1516,6 +1515,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-08-18</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På torrgran.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1543,10 +1547,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120046554</v>
+        <v>120046814</v>
       </c>
       <c r="B10" t="n">
-        <v>79652</v>
+        <v>78542</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1555,25 +1559,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1586,10 +1590,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>454274</v>
+        <v>454172</v>
       </c>
       <c r="R10" t="n">
-        <v>7170002</v>
+        <v>7170015</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1626,7 +1630,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På klen rönn.</t>
+          <t>På grangrenar.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1647,17 +1651,17 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Stefan Björklund, Henrik Tykosson</t>
+          <t>Henrik Tykosson, Stefan Björklund, Bo Törnquist</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120046876</v>
+        <v>120046421</v>
       </c>
       <c r="B11" t="n">
-        <v>97829</v>
+        <v>98265</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1670,21 +1674,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219795</v>
+        <v>219880</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1698,10 +1702,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>454180</v>
+        <v>454365</v>
       </c>
       <c r="R11" t="n">
-        <v>7170065</v>
+        <v>7169956</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1761,10 +1765,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120046948</v>
+        <v>120046668</v>
       </c>
       <c r="B12" t="n">
-        <v>97953</v>
+        <v>79624</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1773,31 +1777,30 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219847</v>
+        <v>2081</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1805,10 +1808,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>454190</v>
+        <v>454160</v>
       </c>
       <c r="R12" t="n">
-        <v>7170110</v>
+        <v>7169971</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1841,6 +1844,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-08-18</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1868,10 +1876,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120046602</v>
+        <v>120046564</v>
       </c>
       <c r="B13" t="n">
-        <v>90545</v>
+        <v>91565</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1884,21 +1892,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>5836</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Guldkremla</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Russula aurea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Pers.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1911,10 +1919,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>454188</v>
+        <v>454274</v>
       </c>
       <c r="R13" t="n">
-        <v>7169986</v>
+        <v>7170002</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1947,11 +1955,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-08-18</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>På granhögstubbe.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1979,10 +1982,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120046587</v>
+        <v>120046702</v>
       </c>
       <c r="B14" t="n">
-        <v>91512</v>
+        <v>78542</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1991,25 +1994,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4769</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2022,10 +2025,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>454254</v>
+        <v>454157</v>
       </c>
       <c r="R14" t="n">
-        <v>7169982</v>
+        <v>7169992</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2058,6 +2061,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-08-18</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På grangrenar.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2085,10 +2093,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120046420</v>
+        <v>120046472</v>
       </c>
       <c r="B15" t="n">
-        <v>78542</v>
+        <v>97951</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2097,30 +2105,31 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2128,10 +2137,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>454365</v>
+        <v>454355</v>
       </c>
       <c r="R15" t="n">
-        <v>7169956</v>
+        <v>7169944</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2164,11 +2173,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-08-18</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På gammal björk.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2196,10 +2200,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120046671</v>
+        <v>120046587</v>
       </c>
       <c r="B16" t="n">
-        <v>79652</v>
+        <v>91512</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2212,21 +2216,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6462</v>
+        <v>4769</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2239,10 +2243,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>454160</v>
+        <v>454254</v>
       </c>
       <c r="R16" t="n">
-        <v>7169971</v>
+        <v>7169982</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2275,11 +2279,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-08-18</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2307,10 +2306,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120046564</v>
+        <v>120046580</v>
       </c>
       <c r="B17" t="n">
-        <v>91565</v>
+        <v>97951</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2323,26 +2322,27 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5836</v>
+        <v>221952</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Guldkremla</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Russula aurea</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Pers.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2350,10 +2350,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>454274</v>
+        <v>454254</v>
       </c>
       <c r="R17" t="n">
-        <v>7170002</v>
+        <v>7169982</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2413,10 +2413,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120046842</v>
+        <v>120046869</v>
       </c>
       <c r="B18" t="n">
-        <v>94274</v>
+        <v>97930</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2425,25 +2425,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>756</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Käppkrokmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hamatocaulis vernicosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Mitt.) Hedenäs</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2457,10 +2457,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>454168</v>
+        <v>454180</v>
       </c>
       <c r="R18" t="n">
-        <v>7170020</v>
+        <v>7170065</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2520,10 +2520,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120046528</v>
+        <v>120046602</v>
       </c>
       <c r="B19" t="n">
-        <v>97829</v>
+        <v>90545</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2536,27 +2536,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219795</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2564,10 +2563,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>454297</v>
+        <v>454188</v>
       </c>
       <c r="R19" t="n">
-        <v>7169982</v>
+        <v>7169986</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2600,6 +2599,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-08-18</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På granhögstubbe.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2627,10 +2631,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120046880</v>
+        <v>120046845</v>
       </c>
       <c r="B20" t="n">
-        <v>97951</v>
+        <v>93766</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2643,21 +2647,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221952</v>
+        <v>2412</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Källmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Philonotis fontana</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2671,10 +2675,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>454180</v>
+        <v>454168</v>
       </c>
       <c r="R20" t="n">
-        <v>7170065</v>
+        <v>7170020</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2734,10 +2738,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120046869</v>
+        <v>120046486</v>
       </c>
       <c r="B21" t="n">
-        <v>97930</v>
+        <v>94334</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2746,25 +2750,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>2809</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2778,10 +2782,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>454180</v>
+        <v>454316</v>
       </c>
       <c r="R21" t="n">
-        <v>7170065</v>
+        <v>7169955</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2841,10 +2845,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120046845</v>
+        <v>120046626</v>
       </c>
       <c r="B22" t="n">
-        <v>93766</v>
+        <v>105017</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2857,21 +2861,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2412</v>
+        <v>221725</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Källmossa</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Philonotis fontana</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2885,10 +2889,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>454168</v>
+        <v>454185</v>
       </c>
       <c r="R22" t="n">
-        <v>7170020</v>
+        <v>7169988</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2948,10 +2952,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120046720</v>
+        <v>120046632</v>
       </c>
       <c r="B23" t="n">
-        <v>90576</v>
+        <v>97847</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2960,30 +2964,31 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1108</v>
+        <v>219790</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2991,10 +2996,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>454158</v>
+        <v>454185</v>
       </c>
       <c r="R23" t="n">
-        <v>7169997</v>
+        <v>7169988</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3027,11 +3032,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-08-18</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>På torrgran.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3059,7 +3059,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120046814</v>
+        <v>120046446</v>
       </c>
       <c r="B24" t="n">
         <v>78542</v>
@@ -3102,10 +3102,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>454172</v>
+        <v>454357</v>
       </c>
       <c r="R24" t="n">
-        <v>7170015</v>
+        <v>7169950</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3170,10 +3170,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120046626</v>
+        <v>120046880</v>
       </c>
       <c r="B25" t="n">
-        <v>105017</v>
+        <v>97951</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3186,21 +3186,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221725</v>
+        <v>221952</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3214,10 +3214,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>454185</v>
+        <v>454180</v>
       </c>
       <c r="R25" t="n">
-        <v>7169988</v>
+        <v>7170065</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3277,10 +3277,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120046446</v>
+        <v>120046554</v>
       </c>
       <c r="B26" t="n">
-        <v>78542</v>
+        <v>79652</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3289,25 +3289,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3320,10 +3320,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>454357</v>
+        <v>454274</v>
       </c>
       <c r="R26" t="n">
-        <v>7169950</v>
+        <v>7170002</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På grangrenar.</t>
+          <t>På klen rönn.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3388,10 +3388,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120046702</v>
+        <v>120046676</v>
       </c>
       <c r="B27" t="n">
-        <v>78542</v>
+        <v>74659</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3404,21 +3404,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3431,10 +3431,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>454157</v>
+        <v>454160</v>
       </c>
       <c r="R27" t="n">
-        <v>7169992</v>
+        <v>7169971</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På grangrenar.</t>
+          <t>På högstubbe av björk.</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 47636-2022 artfynd.xlsx
+++ b/artfynd/A 47636-2022 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120046876</v>
+        <v>120046765</v>
       </c>
       <c r="B3" t="n">
-        <v>97829</v>
+        <v>90598</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,31 +798,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219795</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -830,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>454180</v>
+        <v>454176</v>
       </c>
       <c r="R3" t="n">
-        <v>7170065</v>
+        <v>7170001</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -866,6 +865,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-08-18</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På granlåga.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120046765</v>
+        <v>120046876</v>
       </c>
       <c r="B4" t="n">
-        <v>90598</v>
+        <v>97829</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,30 +909,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>219795</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -936,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>454176</v>
+        <v>454180</v>
       </c>
       <c r="R4" t="n">
-        <v>7170001</v>
+        <v>7170065</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -972,11 +977,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-08-18</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På granlåga.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,10 +1004,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120046528</v>
+        <v>120046842</v>
       </c>
       <c r="B5" t="n">
-        <v>97829</v>
+        <v>94274</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,21 +1020,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219795</v>
+        <v>756</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Käppkrokmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Hamatocaulis vernicosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
+          <t>(Mitt.) Hedenäs</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1048,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>454297</v>
+        <v>454168</v>
       </c>
       <c r="R5" t="n">
-        <v>7169982</v>
+        <v>7170020</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1111,10 +1111,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120046948</v>
+        <v>120046671</v>
       </c>
       <c r="B6" t="n">
-        <v>97953</v>
+        <v>79652</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1127,27 +1127,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219847</v>
+        <v>6462</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1155,10 +1154,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454190</v>
+        <v>454160</v>
       </c>
       <c r="R6" t="n">
-        <v>7170110</v>
+        <v>7169971</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1191,6 +1190,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-08-18</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1218,10 +1222,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120046842</v>
+        <v>120046528</v>
       </c>
       <c r="B7" t="n">
-        <v>94274</v>
+        <v>97829</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1234,21 +1238,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>756</v>
+        <v>219795</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Käppkrokmossa</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hamatocaulis vernicosus</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Mitt.) Hedenäs</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1262,10 +1266,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>454168</v>
+        <v>454297</v>
       </c>
       <c r="R7" t="n">
-        <v>7170020</v>
+        <v>7169982</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1325,10 +1329,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120046671</v>
+        <v>120046948</v>
       </c>
       <c r="B8" t="n">
-        <v>79652</v>
+        <v>97953</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1341,26 +1345,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>219847</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1368,10 +1373,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>454160</v>
+        <v>454190</v>
       </c>
       <c r="R8" t="n">
-        <v>7169971</v>
+        <v>7170110</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1404,11 +1409,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-08-18</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -3170,10 +3170,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120046880</v>
+        <v>120046554</v>
       </c>
       <c r="B25" t="n">
-        <v>97951</v>
+        <v>79652</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3186,27 +3186,26 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221952</v>
+        <v>6462</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3214,10 +3213,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>454180</v>
+        <v>454274</v>
       </c>
       <c r="R25" t="n">
-        <v>7170065</v>
+        <v>7170002</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3250,6 +3249,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-08-18</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>På klen rönn.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3277,10 +3281,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120046554</v>
+        <v>120046676</v>
       </c>
       <c r="B26" t="n">
-        <v>79652</v>
+        <v>74659</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3289,25 +3293,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6462</v>
+        <v>1467</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3320,10 +3324,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>454274</v>
+        <v>454160</v>
       </c>
       <c r="R26" t="n">
-        <v>7170002</v>
+        <v>7169971</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3360,7 +3364,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På klen rönn.</t>
+          <t>På högstubbe av björk.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3388,10 +3392,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120046676</v>
+        <v>120046880</v>
       </c>
       <c r="B27" t="n">
-        <v>74659</v>
+        <v>97951</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3400,30 +3404,31 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1467</v>
+        <v>221952</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3431,10 +3436,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>454160</v>
+        <v>454180</v>
       </c>
       <c r="R27" t="n">
-        <v>7169971</v>
+        <v>7170065</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3467,11 +3472,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-08-18</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>På högstubbe av björk.</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 47636-2022 artfynd.xlsx
+++ b/artfynd/A 47636-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120046420</v>
+        <v>120046421</v>
       </c>
       <c r="B2" t="n">
-        <v>78542</v>
+        <v>98265</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>219880</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -754,11 +755,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-08-18</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På gammal björk.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120046765</v>
+        <v>120046676</v>
       </c>
       <c r="B3" t="n">
-        <v>90598</v>
+        <v>74659</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>1467</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -829,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>454176</v>
+        <v>454160</v>
       </c>
       <c r="R3" t="n">
-        <v>7170001</v>
+        <v>7169971</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -869,7 +865,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På granlåga.</t>
+          <t>På högstubbe av björk.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,10 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120046876</v>
+        <v>120046420</v>
       </c>
       <c r="B4" t="n">
-        <v>97829</v>
+        <v>78542</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,31 +905,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219795</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -941,10 +936,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>454180</v>
+        <v>454365</v>
       </c>
       <c r="R4" t="n">
-        <v>7170065</v>
+        <v>7169956</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -977,6 +972,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-08-18</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På gammal björk.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,10 +1004,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120046842</v>
+        <v>120046880</v>
       </c>
       <c r="B5" t="n">
-        <v>94274</v>
+        <v>97951</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,21 +1020,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>756</v>
+        <v>221952</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Käppkrokmossa</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hamatocaulis vernicosus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Mitt.) Hedenäs</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1048,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>454168</v>
+        <v>454180</v>
       </c>
       <c r="R5" t="n">
-        <v>7170020</v>
+        <v>7170065</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1111,10 +1111,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120046671</v>
+        <v>120046814</v>
       </c>
       <c r="B6" t="n">
-        <v>79652</v>
+        <v>78542</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,25 +1123,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1154,10 +1154,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454160</v>
+        <v>454172</v>
       </c>
       <c r="R6" t="n">
-        <v>7169971</v>
+        <v>7170015</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På rönn.</t>
+          <t>På grangrenar.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1222,10 +1222,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120046528</v>
+        <v>120046472</v>
       </c>
       <c r="B7" t="n">
-        <v>97829</v>
+        <v>97951</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1238,21 +1238,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219795</v>
+        <v>221952</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1266,10 +1266,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>454297</v>
+        <v>454355</v>
       </c>
       <c r="R7" t="n">
-        <v>7169982</v>
+        <v>7169944</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1329,10 +1329,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120046948</v>
+        <v>120046720</v>
       </c>
       <c r="B8" t="n">
-        <v>97953</v>
+        <v>90576</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1341,31 +1341,30 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219847</v>
+        <v>1108</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1373,10 +1372,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>454190</v>
+        <v>454158</v>
       </c>
       <c r="R8" t="n">
-        <v>7170110</v>
+        <v>7169997</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1409,6 +1408,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-08-18</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På torrgran.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1436,10 +1440,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120046720</v>
+        <v>120046446</v>
       </c>
       <c r="B9" t="n">
-        <v>90576</v>
+        <v>78542</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1452,21 +1456,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1479,10 +1483,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>454158</v>
+        <v>454357</v>
       </c>
       <c r="R9" t="n">
-        <v>7169997</v>
+        <v>7169950</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1519,7 +1523,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På torrgran.</t>
+          <t>På grangrenar.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1547,10 +1551,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120046814</v>
+        <v>120046486</v>
       </c>
       <c r="B10" t="n">
-        <v>78542</v>
+        <v>94334</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1559,30 +1563,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1590,10 +1595,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>454172</v>
+        <v>454316</v>
       </c>
       <c r="R10" t="n">
-        <v>7170015</v>
+        <v>7169955</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1628,11 +1633,6 @@
           <t>2024-08-18</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>På grangrenar.</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1651,17 +1651,17 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Henrik Tykosson, Stefan Björklund, Bo Törnquist</t>
+          <t>Bo Törnquist, Stefan Björklund, Henrik Tykosson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120046421</v>
+        <v>120046554</v>
       </c>
       <c r="B11" t="n">
-        <v>98265</v>
+        <v>79652</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1674,27 +1674,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219880</v>
+        <v>6462</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1702,10 +1701,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>454365</v>
+        <v>454274</v>
       </c>
       <c r="R11" t="n">
-        <v>7169956</v>
+        <v>7170002</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1738,6 +1737,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-08-18</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På klen rönn.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1765,10 +1769,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120046668</v>
+        <v>120046876</v>
       </c>
       <c r="B12" t="n">
-        <v>79624</v>
+        <v>97829</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1777,30 +1781,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2081</v>
+        <v>219795</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1808,10 +1813,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>454160</v>
+        <v>454180</v>
       </c>
       <c r="R12" t="n">
-        <v>7169971</v>
+        <v>7170065</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1844,11 +1849,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-08-18</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1876,10 +1876,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120046564</v>
+        <v>120046869</v>
       </c>
       <c r="B13" t="n">
-        <v>91565</v>
+        <v>97930</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1888,30 +1888,31 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5836</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Guldkremla</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Russula aurea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Pers.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1919,10 +1920,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>454274</v>
+        <v>454180</v>
       </c>
       <c r="R13" t="n">
-        <v>7170002</v>
+        <v>7170065</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1982,10 +1983,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120046702</v>
+        <v>120046564</v>
       </c>
       <c r="B14" t="n">
-        <v>78542</v>
+        <v>91565</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1994,25 +1995,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>5836</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Guldkremla</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Russula aurea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pers.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2025,10 +2026,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>454157</v>
+        <v>454274</v>
       </c>
       <c r="R14" t="n">
-        <v>7169992</v>
+        <v>7170002</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2061,11 +2062,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-08-18</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På grangrenar.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2093,10 +2089,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120046472</v>
+        <v>120046668</v>
       </c>
       <c r="B15" t="n">
-        <v>97951</v>
+        <v>79624</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2105,31 +2101,30 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221952</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2137,10 +2132,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>454355</v>
+        <v>454160</v>
       </c>
       <c r="R15" t="n">
-        <v>7169944</v>
+        <v>7169971</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2173,6 +2168,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-08-18</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2306,10 +2306,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120046580</v>
+        <v>120046702</v>
       </c>
       <c r="B17" t="n">
-        <v>97951</v>
+        <v>78542</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2318,31 +2318,30 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2350,10 +2349,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>454254</v>
+        <v>454157</v>
       </c>
       <c r="R17" t="n">
-        <v>7169982</v>
+        <v>7169992</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2386,6 +2385,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-08-18</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På grangrenar.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2413,10 +2417,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120046869</v>
+        <v>120046765</v>
       </c>
       <c r="B18" t="n">
-        <v>97930</v>
+        <v>90598</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2425,31 +2429,30 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2457,10 +2460,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>454180</v>
+        <v>454176</v>
       </c>
       <c r="R18" t="n">
-        <v>7170065</v>
+        <v>7170001</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2493,6 +2496,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-08-18</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På granlåga.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2520,10 +2528,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120046602</v>
+        <v>120046580</v>
       </c>
       <c r="B19" t="n">
-        <v>90545</v>
+        <v>97951</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2536,26 +2544,27 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>221952</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2563,10 +2572,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>454188</v>
+        <v>454254</v>
       </c>
       <c r="R19" t="n">
-        <v>7169986</v>
+        <v>7169982</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2599,11 +2608,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-08-18</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På granhögstubbe.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2631,10 +2635,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120046845</v>
+        <v>120046842</v>
       </c>
       <c r="B20" t="n">
-        <v>93766</v>
+        <v>94274</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2647,21 +2651,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2412</v>
+        <v>756</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Källmossa</t>
+          <t>Käppkrokmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Philonotis fontana</t>
+          <t>Hamatocaulis vernicosus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Mitt.) Hedenäs</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2738,10 +2742,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120046486</v>
+        <v>120046845</v>
       </c>
       <c r="B21" t="n">
-        <v>94334</v>
+        <v>93766</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2754,21 +2758,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2809</v>
+        <v>2412</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Källmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Philonotis fontana</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2782,10 +2786,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>454316</v>
+        <v>454168</v>
       </c>
       <c r="R21" t="n">
-        <v>7169955</v>
+        <v>7170020</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2845,10 +2849,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120046626</v>
+        <v>120046632</v>
       </c>
       <c r="B22" t="n">
-        <v>105017</v>
+        <v>97847</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2861,21 +2865,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221725</v>
+        <v>219790</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2952,10 +2956,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120046632</v>
+        <v>120046626</v>
       </c>
       <c r="B23" t="n">
-        <v>97847</v>
+        <v>105017</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2968,21 +2972,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219790</v>
+        <v>221725</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3059,10 +3063,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120046446</v>
+        <v>120046602</v>
       </c>
       <c r="B24" t="n">
-        <v>78542</v>
+        <v>90545</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3071,25 +3075,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3102,10 +3106,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>454357</v>
+        <v>454188</v>
       </c>
       <c r="R24" t="n">
-        <v>7169950</v>
+        <v>7169986</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3142,7 +3146,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På grangrenar.</t>
+          <t>På granhögstubbe.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3170,10 +3174,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120046554</v>
+        <v>120046528</v>
       </c>
       <c r="B25" t="n">
-        <v>79652</v>
+        <v>97829</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3186,26 +3190,27 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6462</v>
+        <v>219795</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3213,10 +3218,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>454274</v>
+        <v>454297</v>
       </c>
       <c r="R25" t="n">
-        <v>7170002</v>
+        <v>7169982</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3249,11 +3254,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-08-18</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>På klen rönn.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3281,10 +3281,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120046676</v>
+        <v>120046671</v>
       </c>
       <c r="B26" t="n">
-        <v>74659</v>
+        <v>79652</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3293,25 +3293,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1467</v>
+        <v>6462</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3364,7 +3364,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På högstubbe av björk.</t>
+          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3392,10 +3392,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120046880</v>
+        <v>120046948</v>
       </c>
       <c r="B27" t="n">
-        <v>97951</v>
+        <v>97953</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3408,21 +3408,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221952</v>
+        <v>219847</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3436,10 +3436,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>454180</v>
+        <v>454190</v>
       </c>
       <c r="R27" t="n">
-        <v>7170065</v>
+        <v>7170110</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>

--- a/artfynd/A 47636-2022 artfynd.xlsx
+++ b/artfynd/A 47636-2022 artfynd.xlsx
@@ -1440,10 +1440,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120046446</v>
+        <v>120046486</v>
       </c>
       <c r="B9" t="n">
-        <v>78542</v>
+        <v>94334</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1452,30 +1452,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1483,10 +1484,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>454357</v>
+        <v>454316</v>
       </c>
       <c r="R9" t="n">
-        <v>7169950</v>
+        <v>7169955</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1519,11 +1520,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-08-18</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På grangrenar.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1551,10 +1547,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120046486</v>
+        <v>120046446</v>
       </c>
       <c r="B10" t="n">
-        <v>94334</v>
+        <v>78542</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1563,31 +1559,30 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2809</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1595,10 +1590,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>454316</v>
+        <v>454357</v>
       </c>
       <c r="R10" t="n">
-        <v>7169955</v>
+        <v>7169950</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1631,6 +1626,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-08-18</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På grangrenar.</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 47636-2022 artfynd.xlsx
+++ b/artfynd/A 47636-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120046421</v>
+        <v>120046702</v>
       </c>
       <c r="B2" t="n">
-        <v>98265</v>
+        <v>78542</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219880</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>454365</v>
+        <v>454157</v>
       </c>
       <c r="R2" t="n">
-        <v>7169956</v>
+        <v>7169992</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -755,6 +754,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-08-18</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På grangrenar.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120046676</v>
+        <v>120046720</v>
       </c>
       <c r="B3" t="n">
-        <v>74659</v>
+        <v>90576</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1467</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -825,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>454160</v>
+        <v>454158</v>
       </c>
       <c r="R3" t="n">
-        <v>7169971</v>
+        <v>7169997</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -865,7 +869,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På högstubbe av björk.</t>
+          <t>På torrgran.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120046420</v>
+        <v>120046880</v>
       </c>
       <c r="B4" t="n">
-        <v>78542</v>
+        <v>97951</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,30 +909,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -936,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>454365</v>
+        <v>454180</v>
       </c>
       <c r="R4" t="n">
-        <v>7169956</v>
+        <v>7170065</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -972,11 +977,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-08-18</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På gammal björk.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,10 +1004,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120046880</v>
+        <v>120046869</v>
       </c>
       <c r="B5" t="n">
-        <v>97951</v>
+        <v>97930</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1016,25 +1016,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1111,10 +1111,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120046814</v>
+        <v>120046626</v>
       </c>
       <c r="B6" t="n">
-        <v>78542</v>
+        <v>105017</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,30 +1123,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>221725</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1154,10 +1155,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454172</v>
+        <v>454185</v>
       </c>
       <c r="R6" t="n">
-        <v>7170015</v>
+        <v>7169988</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1190,11 +1191,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-08-18</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På grangrenar.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1222,10 +1218,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120046472</v>
+        <v>120046842</v>
       </c>
       <c r="B7" t="n">
-        <v>97951</v>
+        <v>94274</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1238,21 +1234,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221952</v>
+        <v>756</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Käppkrokmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Hamatocaulis vernicosus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Mitt.) Hedenäs</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1266,10 +1262,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>454355</v>
+        <v>454168</v>
       </c>
       <c r="R7" t="n">
-        <v>7169944</v>
+        <v>7170020</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1329,10 +1325,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120046720</v>
+        <v>120046446</v>
       </c>
       <c r="B8" t="n">
-        <v>90576</v>
+        <v>78542</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1345,21 +1341,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1372,10 +1368,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>454158</v>
+        <v>454357</v>
       </c>
       <c r="R8" t="n">
-        <v>7169997</v>
+        <v>7169950</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1412,7 +1408,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På torrgran.</t>
+          <t>På grangrenar.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1440,10 +1436,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120046486</v>
+        <v>120046876</v>
       </c>
       <c r="B9" t="n">
-        <v>94334</v>
+        <v>97829</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1456,21 +1452,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2809</v>
+        <v>219795</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1484,10 +1480,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>454316</v>
+        <v>454180</v>
       </c>
       <c r="R9" t="n">
-        <v>7169955</v>
+        <v>7170065</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1547,10 +1543,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120046446</v>
+        <v>120046564</v>
       </c>
       <c r="B10" t="n">
-        <v>78542</v>
+        <v>91565</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1559,25 +1555,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>5836</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Guldkremla</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Russula aurea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pers.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1590,10 +1586,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>454357</v>
+        <v>454274</v>
       </c>
       <c r="R10" t="n">
-        <v>7169950</v>
+        <v>7170002</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1626,11 +1622,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-08-18</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>På grangrenar.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1658,10 +1649,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120046554</v>
+        <v>120046528</v>
       </c>
       <c r="B11" t="n">
-        <v>79652</v>
+        <v>97829</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1674,26 +1665,27 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6462</v>
+        <v>219795</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1701,10 +1693,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>454274</v>
+        <v>454297</v>
       </c>
       <c r="R11" t="n">
-        <v>7170002</v>
+        <v>7169982</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1737,11 +1729,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-08-18</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>På klen rönn.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1769,10 +1756,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120046876</v>
+        <v>120046486</v>
       </c>
       <c r="B12" t="n">
-        <v>97829</v>
+        <v>94334</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1785,21 +1772,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219795</v>
+        <v>2809</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1813,10 +1800,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>454180</v>
+        <v>454316</v>
       </c>
       <c r="R12" t="n">
-        <v>7170065</v>
+        <v>7169955</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1876,10 +1863,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120046869</v>
+        <v>120046948</v>
       </c>
       <c r="B13" t="n">
-        <v>97930</v>
+        <v>97953</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1888,25 +1875,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>219847</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1920,10 +1907,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>454180</v>
+        <v>454190</v>
       </c>
       <c r="R13" t="n">
-        <v>7170065</v>
+        <v>7170110</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1983,10 +1970,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120046564</v>
+        <v>120046671</v>
       </c>
       <c r="B14" t="n">
-        <v>91565</v>
+        <v>79652</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1999,21 +1986,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5836</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Guldkremla</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Russula aurea</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Pers.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2026,10 +2013,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>454274</v>
+        <v>454160</v>
       </c>
       <c r="R14" t="n">
-        <v>7170002</v>
+        <v>7169971</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2062,6 +2049,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-08-18</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2089,10 +2081,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120046668</v>
+        <v>120046632</v>
       </c>
       <c r="B15" t="n">
-        <v>79624</v>
+        <v>97847</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2101,30 +2093,31 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2081</v>
+        <v>219790</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2132,10 +2125,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>454160</v>
+        <v>454185</v>
       </c>
       <c r="R15" t="n">
-        <v>7169971</v>
+        <v>7169988</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2168,11 +2161,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-08-18</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2200,10 +2188,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120046587</v>
+        <v>120046845</v>
       </c>
       <c r="B16" t="n">
-        <v>91512</v>
+        <v>93766</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2216,26 +2204,27 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4769</v>
+        <v>2412</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Källmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Philonotis fontana</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2243,10 +2232,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>454254</v>
+        <v>454168</v>
       </c>
       <c r="R16" t="n">
-        <v>7169982</v>
+        <v>7170020</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2306,10 +2295,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120046702</v>
+        <v>120046554</v>
       </c>
       <c r="B17" t="n">
-        <v>78542</v>
+        <v>79652</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2318,25 +2307,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2349,10 +2338,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>454157</v>
+        <v>454274</v>
       </c>
       <c r="R17" t="n">
-        <v>7169992</v>
+        <v>7170002</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2389,7 +2378,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På grangrenar.</t>
+          <t>På klen rönn.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2417,10 +2406,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120046765</v>
+        <v>120046421</v>
       </c>
       <c r="B18" t="n">
-        <v>90598</v>
+        <v>98265</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2429,30 +2418,31 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>219880</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2460,10 +2450,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>454176</v>
+        <v>454365</v>
       </c>
       <c r="R18" t="n">
-        <v>7170001</v>
+        <v>7169956</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2496,11 +2486,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-08-18</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På granlåga.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2528,10 +2513,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120046580</v>
+        <v>120046668</v>
       </c>
       <c r="B19" t="n">
-        <v>97951</v>
+        <v>79624</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2540,31 +2525,30 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221952</v>
+        <v>2081</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2572,10 +2556,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>454254</v>
+        <v>454160</v>
       </c>
       <c r="R19" t="n">
-        <v>7169982</v>
+        <v>7169971</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2608,6 +2592,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-08-18</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2635,10 +2624,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120046842</v>
+        <v>120046814</v>
       </c>
       <c r="B20" t="n">
-        <v>94274</v>
+        <v>78542</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2647,31 +2636,30 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>756</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Käppkrokmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hamatocaulis vernicosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Mitt.) Hedenäs</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2679,10 +2667,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>454168</v>
+        <v>454172</v>
       </c>
       <c r="R20" t="n">
-        <v>7170020</v>
+        <v>7170015</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2715,6 +2703,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-08-18</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>På grangrenar.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2742,10 +2735,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120046845</v>
+        <v>120046765</v>
       </c>
       <c r="B21" t="n">
-        <v>93766</v>
+        <v>90598</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2754,31 +2747,30 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2412</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Källmossa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Philonotis fontana</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2786,10 +2778,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>454168</v>
+        <v>454176</v>
       </c>
       <c r="R21" t="n">
-        <v>7170020</v>
+        <v>7170001</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2822,6 +2814,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-08-18</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På granlåga.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2849,10 +2846,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120046632</v>
+        <v>120046472</v>
       </c>
       <c r="B22" t="n">
-        <v>97847</v>
+        <v>97951</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2865,21 +2862,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219790</v>
+        <v>221952</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2893,10 +2890,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>454185</v>
+        <v>454355</v>
       </c>
       <c r="R22" t="n">
-        <v>7169988</v>
+        <v>7169944</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2956,10 +2953,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120046626</v>
+        <v>120046580</v>
       </c>
       <c r="B23" t="n">
-        <v>105017</v>
+        <v>97951</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2972,21 +2969,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221725</v>
+        <v>221952</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3000,10 +2997,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>454185</v>
+        <v>454254</v>
       </c>
       <c r="R23" t="n">
-        <v>7169988</v>
+        <v>7169982</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3063,10 +3060,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120046602</v>
+        <v>120046587</v>
       </c>
       <c r="B24" t="n">
-        <v>90545</v>
+        <v>91512</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3079,21 +3076,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>4769</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3106,10 +3103,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>454188</v>
+        <v>454254</v>
       </c>
       <c r="R24" t="n">
-        <v>7169986</v>
+        <v>7169982</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3142,11 +3139,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-08-18</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>På granhögstubbe.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3174,10 +3166,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120046528</v>
+        <v>120046676</v>
       </c>
       <c r="B25" t="n">
-        <v>97829</v>
+        <v>74659</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3186,31 +3178,30 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>219795</v>
+        <v>1467</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3218,10 +3209,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>454297</v>
+        <v>454160</v>
       </c>
       <c r="R25" t="n">
-        <v>7169982</v>
+        <v>7169971</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3254,6 +3245,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-08-18</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>På högstubbe av björk.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3281,10 +3277,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120046671</v>
+        <v>120046602</v>
       </c>
       <c r="B26" t="n">
-        <v>79652</v>
+        <v>90545</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3297,21 +3293,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6462</v>
+        <v>5447</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3324,10 +3320,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>454160</v>
+        <v>454188</v>
       </c>
       <c r="R26" t="n">
-        <v>7169971</v>
+        <v>7169986</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3364,7 +3360,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På rönn.</t>
+          <t>På granhögstubbe.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3392,10 +3388,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120046948</v>
+        <v>120046420</v>
       </c>
       <c r="B27" t="n">
-        <v>97953</v>
+        <v>78542</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3404,31 +3400,30 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>219847</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3436,10 +3431,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>454190</v>
+        <v>454365</v>
       </c>
       <c r="R27" t="n">
-        <v>7170110</v>
+        <v>7169956</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3472,6 +3467,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-08-18</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>På gammal björk.</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 47636-2022 artfynd.xlsx
+++ b/artfynd/A 47636-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120046702</v>
+        <v>120046626</v>
       </c>
       <c r="B2" t="n">
-        <v>78542</v>
+        <v>105017</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>221725</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>454157</v>
+        <v>454185</v>
       </c>
       <c r="R2" t="n">
-        <v>7169992</v>
+        <v>7169988</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -754,11 +755,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-08-18</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På grangrenar.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120046720</v>
+        <v>120046528</v>
       </c>
       <c r="B3" t="n">
-        <v>90576</v>
+        <v>97829</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,30 +794,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1108</v>
+        <v>219795</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -829,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>454158</v>
+        <v>454297</v>
       </c>
       <c r="R3" t="n">
-        <v>7169997</v>
+        <v>7169982</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -865,11 +862,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-08-18</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På torrgran.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120046880</v>
+        <v>120046869</v>
       </c>
       <c r="B4" t="n">
-        <v>97951</v>
+        <v>97930</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,25 +901,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -1004,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120046869</v>
+        <v>120046876</v>
       </c>
       <c r="B5" t="n">
-        <v>97930</v>
+        <v>97829</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1016,25 +1008,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>219795</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1111,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120046626</v>
+        <v>120046446</v>
       </c>
       <c r="B6" t="n">
-        <v>105017</v>
+        <v>78542</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,31 +1115,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221725</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1155,10 +1146,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454185</v>
+        <v>454357</v>
       </c>
       <c r="R6" t="n">
-        <v>7169988</v>
+        <v>7169950</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1191,6 +1182,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-08-18</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På grangrenar.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1218,10 +1214,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120046842</v>
+        <v>120046720</v>
       </c>
       <c r="B7" t="n">
-        <v>94274</v>
+        <v>90576</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1230,31 +1226,30 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>756</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Käppkrokmossa</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hamatocaulis vernicosus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Mitt.) Hedenäs</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1262,10 +1257,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>454168</v>
+        <v>454158</v>
       </c>
       <c r="R7" t="n">
-        <v>7170020</v>
+        <v>7169997</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1298,6 +1293,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-08-18</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På torrgran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1325,10 +1325,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120046446</v>
+        <v>120046880</v>
       </c>
       <c r="B8" t="n">
-        <v>78542</v>
+        <v>97951</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1337,30 +1337,31 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1368,10 +1369,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>454357</v>
+        <v>454180</v>
       </c>
       <c r="R8" t="n">
-        <v>7169950</v>
+        <v>7170065</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1404,11 +1405,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-08-18</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På grangrenar.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1436,10 +1432,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120046876</v>
+        <v>120046702</v>
       </c>
       <c r="B9" t="n">
-        <v>97829</v>
+        <v>78542</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1448,31 +1444,30 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219795</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1480,10 +1475,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>454180</v>
+        <v>454157</v>
       </c>
       <c r="R9" t="n">
-        <v>7170065</v>
+        <v>7169992</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1516,6 +1511,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-08-18</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På grangrenar.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1543,10 +1543,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120046564</v>
+        <v>120046420</v>
       </c>
       <c r="B10" t="n">
-        <v>91565</v>
+        <v>78542</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1555,25 +1555,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5836</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Guldkremla</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Russula aurea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Pers.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1586,10 +1586,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>454274</v>
+        <v>454365</v>
       </c>
       <c r="R10" t="n">
-        <v>7170002</v>
+        <v>7169956</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1622,6 +1622,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-08-18</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På gammal björk.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1649,10 +1654,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120046528</v>
+        <v>120046587</v>
       </c>
       <c r="B11" t="n">
-        <v>97829</v>
+        <v>91512</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1665,27 +1670,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219795</v>
+        <v>4769</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1693,7 +1697,7 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>454297</v>
+        <v>454254</v>
       </c>
       <c r="R11" t="n">
         <v>7169982</v>
@@ -1756,10 +1760,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120046486</v>
+        <v>120046632</v>
       </c>
       <c r="B12" t="n">
-        <v>94334</v>
+        <v>97847</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1772,21 +1776,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2809</v>
+        <v>219790</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1800,10 +1804,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>454316</v>
+        <v>454185</v>
       </c>
       <c r="R12" t="n">
-        <v>7169955</v>
+        <v>7169988</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1863,10 +1867,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120046948</v>
+        <v>120046472</v>
       </c>
       <c r="B13" t="n">
-        <v>97953</v>
+        <v>97951</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1879,21 +1883,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219847</v>
+        <v>221952</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1907,10 +1911,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>454190</v>
+        <v>454355</v>
       </c>
       <c r="R13" t="n">
-        <v>7170110</v>
+        <v>7169944</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1970,10 +1974,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120046671</v>
+        <v>120046845</v>
       </c>
       <c r="B14" t="n">
-        <v>79652</v>
+        <v>93766</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1986,26 +1990,27 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6462</v>
+        <v>2412</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Källmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Philonotis fontana</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2013,10 +2018,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>454160</v>
+        <v>454168</v>
       </c>
       <c r="R14" t="n">
-        <v>7169971</v>
+        <v>7170020</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2049,11 +2054,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-08-18</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2081,10 +2081,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120046632</v>
+        <v>120046671</v>
       </c>
       <c r="B15" t="n">
-        <v>97847</v>
+        <v>79652</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2097,27 +2097,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219790</v>
+        <v>6462</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2125,10 +2124,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>454185</v>
+        <v>454160</v>
       </c>
       <c r="R15" t="n">
-        <v>7169988</v>
+        <v>7169971</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2161,6 +2160,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-08-18</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2188,10 +2192,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120046845</v>
+        <v>120046421</v>
       </c>
       <c r="B16" t="n">
-        <v>93766</v>
+        <v>98265</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2204,21 +2208,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2412</v>
+        <v>219880</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Källmossa</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Philonotis fontana</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2232,10 +2236,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>454168</v>
+        <v>454365</v>
       </c>
       <c r="R16" t="n">
-        <v>7170020</v>
+        <v>7169956</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2295,10 +2299,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120046554</v>
+        <v>120046765</v>
       </c>
       <c r="B17" t="n">
-        <v>79652</v>
+        <v>90598</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2307,25 +2311,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2338,10 +2342,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>454274</v>
+        <v>454176</v>
       </c>
       <c r="R17" t="n">
-        <v>7170002</v>
+        <v>7170001</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2378,7 +2382,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På klen rönn.</t>
+          <t>På granlåga.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2406,10 +2410,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120046421</v>
+        <v>120046842</v>
       </c>
       <c r="B18" t="n">
-        <v>98265</v>
+        <v>94274</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2422,21 +2426,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219880</v>
+        <v>756</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Käppkrokmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Hamatocaulis vernicosus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Mitt.) Hedenäs</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2450,10 +2454,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>454365</v>
+        <v>454168</v>
       </c>
       <c r="R18" t="n">
-        <v>7169956</v>
+        <v>7170020</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2513,10 +2517,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120046668</v>
+        <v>120046676</v>
       </c>
       <c r="B19" t="n">
-        <v>79624</v>
+        <v>74659</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2529,21 +2533,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2081</v>
+        <v>1467</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2596,7 +2600,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På rönn.</t>
+          <t>På högstubbe av björk.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2624,10 +2628,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120046814</v>
+        <v>120046554</v>
       </c>
       <c r="B20" t="n">
-        <v>78542</v>
+        <v>79652</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2636,25 +2640,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2667,10 +2671,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>454172</v>
+        <v>454274</v>
       </c>
       <c r="R20" t="n">
-        <v>7170015</v>
+        <v>7170002</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2707,7 +2711,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På grangrenar.</t>
+          <t>På klen rönn.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2735,10 +2739,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120046765</v>
+        <v>120046948</v>
       </c>
       <c r="B21" t="n">
-        <v>90598</v>
+        <v>97953</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2747,30 +2751,31 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>219847</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2778,10 +2783,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>454176</v>
+        <v>454190</v>
       </c>
       <c r="R21" t="n">
-        <v>7170001</v>
+        <v>7170110</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2814,11 +2819,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-08-18</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>På granlåga.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2846,10 +2846,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120046472</v>
+        <v>120046668</v>
       </c>
       <c r="B22" t="n">
-        <v>97951</v>
+        <v>79624</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2858,31 +2858,30 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221952</v>
+        <v>2081</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2890,10 +2889,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>454355</v>
+        <v>454160</v>
       </c>
       <c r="R22" t="n">
-        <v>7169944</v>
+        <v>7169971</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2926,6 +2925,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-08-18</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2953,10 +2957,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120046580</v>
+        <v>120046814</v>
       </c>
       <c r="B23" t="n">
-        <v>97951</v>
+        <v>78542</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2965,31 +2969,30 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2997,10 +3000,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>454254</v>
+        <v>454172</v>
       </c>
       <c r="R23" t="n">
-        <v>7169982</v>
+        <v>7170015</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3033,6 +3036,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-08-18</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>På grangrenar.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3060,10 +3068,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120046587</v>
+        <v>120046580</v>
       </c>
       <c r="B24" t="n">
-        <v>91512</v>
+        <v>97951</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3076,26 +3084,27 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4769</v>
+        <v>221952</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3166,10 +3175,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120046676</v>
+        <v>120046486</v>
       </c>
       <c r="B25" t="n">
-        <v>74659</v>
+        <v>94334</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3178,30 +3187,31 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1467</v>
+        <v>2809</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3209,10 +3219,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>454160</v>
+        <v>454316</v>
       </c>
       <c r="R25" t="n">
-        <v>7169971</v>
+        <v>7169955</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3245,11 +3255,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-08-18</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>På högstubbe av björk.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3388,10 +3393,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120046420</v>
+        <v>120046564</v>
       </c>
       <c r="B27" t="n">
-        <v>78542</v>
+        <v>91565</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3400,25 +3405,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>5836</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Guldkremla</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Russula aurea</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pers.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3431,10 +3436,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>454365</v>
+        <v>454274</v>
       </c>
       <c r="R27" t="n">
-        <v>7169956</v>
+        <v>7170002</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3467,11 +3472,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-08-18</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>På gammal björk.</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 47636-2022 artfynd.xlsx
+++ b/artfynd/A 47636-2022 artfynd.xlsx
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120046446</v>
+        <v>120046720</v>
       </c>
       <c r="B6" t="n">
-        <v>78542</v>
+        <v>90576</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1119,21 +1119,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1146,10 +1146,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454357</v>
+        <v>454158</v>
       </c>
       <c r="R6" t="n">
-        <v>7169950</v>
+        <v>7169997</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På grangrenar.</t>
+          <t>På torrgran.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1214,10 +1214,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120046720</v>
+        <v>120046446</v>
       </c>
       <c r="B7" t="n">
-        <v>90576</v>
+        <v>78542</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1230,21 +1230,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1257,10 +1257,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>454158</v>
+        <v>454357</v>
       </c>
       <c r="R7" t="n">
-        <v>7169997</v>
+        <v>7169950</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1297,7 +1297,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På torrgran.</t>
+          <t>På grangrenar.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1760,10 +1760,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120046632</v>
+        <v>120046472</v>
       </c>
       <c r="B12" t="n">
-        <v>97847</v>
+        <v>97951</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1776,21 +1776,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219790</v>
+        <v>221952</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1804,10 +1804,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>454185</v>
+        <v>454355</v>
       </c>
       <c r="R12" t="n">
-        <v>7169988</v>
+        <v>7169944</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1867,10 +1867,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120046472</v>
+        <v>120046632</v>
       </c>
       <c r="B13" t="n">
-        <v>97951</v>
+        <v>97847</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1883,21 +1883,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221952</v>
+        <v>219790</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1911,10 +1911,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>454355</v>
+        <v>454185</v>
       </c>
       <c r="R13" t="n">
-        <v>7169944</v>
+        <v>7169988</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2628,10 +2628,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120046554</v>
+        <v>120046948</v>
       </c>
       <c r="B20" t="n">
-        <v>79652</v>
+        <v>97953</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2644,26 +2644,27 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6462</v>
+        <v>219847</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2671,10 +2672,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>454274</v>
+        <v>454190</v>
       </c>
       <c r="R20" t="n">
-        <v>7170002</v>
+        <v>7170110</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2707,11 +2708,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-08-18</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>På klen rönn.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2739,10 +2735,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120046948</v>
+        <v>120046554</v>
       </c>
       <c r="B21" t="n">
-        <v>97953</v>
+        <v>79652</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2755,27 +2751,26 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219847</v>
+        <v>6462</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2783,10 +2778,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>454190</v>
+        <v>454274</v>
       </c>
       <c r="R21" t="n">
-        <v>7170110</v>
+        <v>7170002</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2819,6 +2814,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-08-18</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På klen rönn.</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 47636-2022 artfynd.xlsx
+++ b/artfynd/A 47636-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120046626</v>
+        <v>120046486</v>
       </c>
       <c r="B2" t="n">
-        <v>105017</v>
+        <v>94334</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221725</v>
+        <v>2809</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>454185</v>
+        <v>454316</v>
       </c>
       <c r="R2" t="n">
-        <v>7169988</v>
+        <v>7169955</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120046528</v>
+        <v>120046626</v>
       </c>
       <c r="B3" t="n">
-        <v>97829</v>
+        <v>105017</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219795</v>
+        <v>221725</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>454297</v>
+        <v>454185</v>
       </c>
       <c r="R3" t="n">
-        <v>7169982</v>
+        <v>7169988</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120046869</v>
+        <v>120046880</v>
       </c>
       <c r="B4" t="n">
-        <v>97930</v>
+        <v>97951</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,25 +901,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120046876</v>
+        <v>120046421</v>
       </c>
       <c r="B5" t="n">
-        <v>97829</v>
+        <v>98265</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,21 +1012,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219795</v>
+        <v>219880</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>454180</v>
+        <v>454365</v>
       </c>
       <c r="R5" t="n">
-        <v>7170065</v>
+        <v>7169956</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120046720</v>
+        <v>120046842</v>
       </c>
       <c r="B6" t="n">
-        <v>90576</v>
+        <v>94274</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,30 +1115,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>756</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Käppkrokmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Hamatocaulis vernicosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Mitt.) Hedenäs</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1146,10 +1147,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454158</v>
+        <v>454168</v>
       </c>
       <c r="R6" t="n">
-        <v>7169997</v>
+        <v>7170020</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1182,11 +1183,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-08-18</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På torrgran.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1214,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120046446</v>
+        <v>120046632</v>
       </c>
       <c r="B7" t="n">
-        <v>78542</v>
+        <v>97847</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1226,30 +1222,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1257,10 +1254,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>454357</v>
+        <v>454185</v>
       </c>
       <c r="R7" t="n">
-        <v>7169950</v>
+        <v>7169988</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1293,11 +1290,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-08-18</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På grangrenar.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1325,7 +1317,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120046880</v>
+        <v>120046472</v>
       </c>
       <c r="B8" t="n">
         <v>97951</v>
@@ -1369,10 +1361,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>454180</v>
+        <v>454355</v>
       </c>
       <c r="R8" t="n">
-        <v>7170065</v>
+        <v>7169944</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1432,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120046702</v>
+        <v>120046676</v>
       </c>
       <c r="B9" t="n">
-        <v>78542</v>
+        <v>74659</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1448,21 +1440,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1475,10 +1467,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>454157</v>
+        <v>454160</v>
       </c>
       <c r="R9" t="n">
-        <v>7169992</v>
+        <v>7169971</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1515,7 +1507,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På grangrenar.</t>
+          <t>På högstubbe av björk.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1543,10 +1535,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120046420</v>
+        <v>120046668</v>
       </c>
       <c r="B10" t="n">
-        <v>78542</v>
+        <v>79624</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1559,21 +1551,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1586,10 +1578,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>454365</v>
+        <v>454160</v>
       </c>
       <c r="R10" t="n">
-        <v>7169956</v>
+        <v>7169971</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1626,7 +1618,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På gammal björk.</t>
+          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1654,10 +1646,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120046587</v>
+        <v>120046580</v>
       </c>
       <c r="B11" t="n">
-        <v>91512</v>
+        <v>97951</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1670,26 +1662,27 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4769</v>
+        <v>221952</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1760,10 +1753,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120046472</v>
+        <v>120046948</v>
       </c>
       <c r="B12" t="n">
-        <v>97951</v>
+        <v>97953</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1776,21 +1769,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221952</v>
+        <v>219847</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1804,10 +1797,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>454355</v>
+        <v>454190</v>
       </c>
       <c r="R12" t="n">
-        <v>7169944</v>
+        <v>7170110</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1867,10 +1860,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120046632</v>
+        <v>120046602</v>
       </c>
       <c r="B13" t="n">
-        <v>97847</v>
+        <v>90545</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1883,27 +1876,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219790</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1911,10 +1903,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>454185</v>
+        <v>454188</v>
       </c>
       <c r="R13" t="n">
-        <v>7169988</v>
+        <v>7169986</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1947,6 +1939,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-08-18</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På granhögstubbe.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1974,10 +1971,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120046845</v>
+        <v>120046564</v>
       </c>
       <c r="B14" t="n">
-        <v>93766</v>
+        <v>91565</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1990,27 +1987,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2412</v>
+        <v>5836</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Källmossa</t>
+          <t>Guldkremla</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Philonotis fontana</t>
+          <t>Russula aurea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>Pers.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2018,10 +2014,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>454168</v>
+        <v>454274</v>
       </c>
       <c r="R14" t="n">
-        <v>7170020</v>
+        <v>7170002</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2081,10 +2077,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120046671</v>
+        <v>120046420</v>
       </c>
       <c r="B15" t="n">
-        <v>79652</v>
+        <v>78542</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2093,25 +2089,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2124,10 +2120,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>454160</v>
+        <v>454365</v>
       </c>
       <c r="R15" t="n">
-        <v>7169971</v>
+        <v>7169956</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2164,7 +2160,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På rönn.</t>
+          <t>På gammal björk.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2192,10 +2188,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120046421</v>
+        <v>120046446</v>
       </c>
       <c r="B16" t="n">
-        <v>98265</v>
+        <v>78542</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2204,31 +2200,30 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219880</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2236,10 +2231,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>454365</v>
+        <v>454357</v>
       </c>
       <c r="R16" t="n">
-        <v>7169956</v>
+        <v>7169950</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2272,6 +2267,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-08-18</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På grangrenar.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2299,10 +2299,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120046765</v>
+        <v>120046720</v>
       </c>
       <c r="B17" t="n">
-        <v>90598</v>
+        <v>90576</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2315,21 +2315,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2342,10 +2342,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>454176</v>
+        <v>454158</v>
       </c>
       <c r="R17" t="n">
-        <v>7170001</v>
+        <v>7169997</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På granlåga.</t>
+          <t>På torrgran.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2410,10 +2410,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120046842</v>
+        <v>120046814</v>
       </c>
       <c r="B18" t="n">
-        <v>94274</v>
+        <v>78542</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2422,31 +2422,30 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>756</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Käppkrokmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hamatocaulis vernicosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Mitt.) Hedenäs</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2454,10 +2453,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>454168</v>
+        <v>454172</v>
       </c>
       <c r="R18" t="n">
-        <v>7170020</v>
+        <v>7170015</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2490,6 +2489,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-08-18</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På grangrenar.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2517,10 +2521,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120046676</v>
+        <v>120046702</v>
       </c>
       <c r="B19" t="n">
-        <v>74659</v>
+        <v>78542</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2533,21 +2537,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2560,10 +2564,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>454160</v>
+        <v>454157</v>
       </c>
       <c r="R19" t="n">
-        <v>7169971</v>
+        <v>7169992</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2600,7 +2604,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På högstubbe av björk.</t>
+          <t>På grangrenar.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2628,10 +2632,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120046948</v>
+        <v>120046554</v>
       </c>
       <c r="B20" t="n">
-        <v>97953</v>
+        <v>79652</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2644,27 +2648,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219847</v>
+        <v>6462</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2672,10 +2675,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>454190</v>
+        <v>454274</v>
       </c>
       <c r="R20" t="n">
-        <v>7170110</v>
+        <v>7170002</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2708,6 +2711,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-08-18</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>På klen rönn.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2735,10 +2743,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120046554</v>
+        <v>120046876</v>
       </c>
       <c r="B21" t="n">
-        <v>79652</v>
+        <v>97829</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2751,26 +2759,27 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6462</v>
+        <v>219795</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2778,10 +2787,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>454274</v>
+        <v>454180</v>
       </c>
       <c r="R21" t="n">
-        <v>7170002</v>
+        <v>7170065</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2814,11 +2823,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-08-18</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>På klen rönn.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2846,10 +2850,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120046668</v>
+        <v>120046587</v>
       </c>
       <c r="B22" t="n">
-        <v>79624</v>
+        <v>91512</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2858,25 +2862,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2081</v>
+        <v>4769</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2889,10 +2893,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>454160</v>
+        <v>454254</v>
       </c>
       <c r="R22" t="n">
-        <v>7169971</v>
+        <v>7169982</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2925,11 +2929,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-08-18</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2957,10 +2956,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120046814</v>
+        <v>120046845</v>
       </c>
       <c r="B23" t="n">
-        <v>78542</v>
+        <v>93766</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2969,30 +2968,31 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>2412</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Källmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Philonotis fontana</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3000,10 +3000,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>454172</v>
+        <v>454168</v>
       </c>
       <c r="R23" t="n">
-        <v>7170015</v>
+        <v>7170020</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3036,11 +3036,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-08-18</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>På grangrenar.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3068,10 +3063,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120046580</v>
+        <v>120046671</v>
       </c>
       <c r="B24" t="n">
-        <v>97951</v>
+        <v>79652</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3084,27 +3079,26 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221952</v>
+        <v>6462</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3112,10 +3106,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>454254</v>
+        <v>454160</v>
       </c>
       <c r="R24" t="n">
-        <v>7169982</v>
+        <v>7169971</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3148,6 +3142,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-08-18</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3175,10 +3174,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120046486</v>
+        <v>120046765</v>
       </c>
       <c r="B25" t="n">
-        <v>94334</v>
+        <v>90598</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3187,31 +3186,30 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2809</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3219,10 +3217,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>454316</v>
+        <v>454176</v>
       </c>
       <c r="R25" t="n">
-        <v>7169955</v>
+        <v>7170001</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3255,6 +3253,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-08-18</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>På granlåga.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3282,10 +3285,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120046602</v>
+        <v>120046869</v>
       </c>
       <c r="B26" t="n">
-        <v>90545</v>
+        <v>97930</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3294,30 +3297,31 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3325,10 +3329,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>454188</v>
+        <v>454180</v>
       </c>
       <c r="R26" t="n">
-        <v>7169986</v>
+        <v>7170065</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3361,11 +3365,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-08-18</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>På granhögstubbe.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3393,10 +3392,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120046564</v>
+        <v>120046528</v>
       </c>
       <c r="B27" t="n">
-        <v>91565</v>
+        <v>97829</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3409,26 +3408,27 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5836</v>
+        <v>219795</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Guldkremla</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Russula aurea</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Pers.</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3436,10 +3436,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>454274</v>
+        <v>454297</v>
       </c>
       <c r="R27" t="n">
-        <v>7170002</v>
+        <v>7169982</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>

--- a/artfynd/A 47636-2022 artfynd.xlsx
+++ b/artfynd/A 47636-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120046486</v>
+        <v>120046668</v>
       </c>
       <c r="B2" t="n">
-        <v>94334</v>
+        <v>79624</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2809</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>454316</v>
+        <v>454160</v>
       </c>
       <c r="R2" t="n">
-        <v>7169955</v>
+        <v>7169971</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -755,6 +754,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-08-18</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120046626</v>
+        <v>120046554</v>
       </c>
       <c r="B3" t="n">
-        <v>105017</v>
+        <v>79652</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,27 +802,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221725</v>
+        <v>6462</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -826,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>454185</v>
+        <v>454274</v>
       </c>
       <c r="R3" t="n">
-        <v>7169988</v>
+        <v>7170002</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -862,6 +865,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-08-18</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På klen rönn.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120046880</v>
+        <v>120046720</v>
       </c>
       <c r="B4" t="n">
-        <v>97951</v>
+        <v>90576</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,31 +909,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221952</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -933,10 +940,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>454180</v>
+        <v>454158</v>
       </c>
       <c r="R4" t="n">
-        <v>7170065</v>
+        <v>7169997</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -969,6 +976,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-08-18</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På torrgran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120046421</v>
+        <v>120046564</v>
       </c>
       <c r="B5" t="n">
-        <v>98265</v>
+        <v>91565</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,27 +1024,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219880</v>
+        <v>5836</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Guldkremla</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Russula aurea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>Pers.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1040,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>454365</v>
+        <v>454274</v>
       </c>
       <c r="R5" t="n">
-        <v>7169956</v>
+        <v>7170002</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1103,10 +1114,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120046842</v>
+        <v>120046421</v>
       </c>
       <c r="B6" t="n">
-        <v>94274</v>
+        <v>98265</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1119,21 +1130,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>756</v>
+        <v>219880</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Käppkrokmossa</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hamatocaulis vernicosus</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Mitt.) Hedenäs</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1147,10 +1158,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454168</v>
+        <v>454365</v>
       </c>
       <c r="R6" t="n">
-        <v>7170020</v>
+        <v>7169956</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1210,10 +1221,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120046632</v>
+        <v>120046671</v>
       </c>
       <c r="B7" t="n">
-        <v>97847</v>
+        <v>79652</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1226,27 +1237,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219790</v>
+        <v>6462</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1254,10 +1264,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>454185</v>
+        <v>454160</v>
       </c>
       <c r="R7" t="n">
-        <v>7169988</v>
+        <v>7169971</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1290,6 +1300,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-08-18</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På rönn.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,10 +1332,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120046472</v>
+        <v>120046446</v>
       </c>
       <c r="B8" t="n">
-        <v>97951</v>
+        <v>78542</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1329,31 +1344,30 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1361,10 +1375,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>454355</v>
+        <v>454357</v>
       </c>
       <c r="R8" t="n">
-        <v>7169944</v>
+        <v>7169950</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1397,6 +1411,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-08-18</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På grangrenar.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,10 +1443,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120046676</v>
+        <v>120046580</v>
       </c>
       <c r="B9" t="n">
-        <v>74659</v>
+        <v>97951</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1436,30 +1455,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1467</v>
+        <v>221952</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1467,10 +1487,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>454160</v>
+        <v>454254</v>
       </c>
       <c r="R9" t="n">
-        <v>7169971</v>
+        <v>7169982</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1503,11 +1523,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-08-18</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På högstubbe av björk.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1535,10 +1550,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120046668</v>
+        <v>120046420</v>
       </c>
       <c r="B10" t="n">
-        <v>79624</v>
+        <v>78542</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1551,21 +1566,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1578,10 +1593,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>454160</v>
+        <v>454365</v>
       </c>
       <c r="R10" t="n">
-        <v>7169971</v>
+        <v>7169956</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1618,7 +1633,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På rönn.</t>
+          <t>På gammal björk.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1646,10 +1661,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120046580</v>
+        <v>120046528</v>
       </c>
       <c r="B11" t="n">
-        <v>97951</v>
+        <v>97829</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1662,21 +1677,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221952</v>
+        <v>219795</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1690,7 +1705,7 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>454254</v>
+        <v>454297</v>
       </c>
       <c r="R11" t="n">
         <v>7169982</v>
@@ -1753,10 +1768,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120046948</v>
+        <v>120046626</v>
       </c>
       <c r="B12" t="n">
-        <v>97953</v>
+        <v>105017</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1769,21 +1784,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219847</v>
+        <v>221725</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1797,10 +1812,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>454190</v>
+        <v>454185</v>
       </c>
       <c r="R12" t="n">
-        <v>7170110</v>
+        <v>7169988</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1860,10 +1875,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120046602</v>
+        <v>120046948</v>
       </c>
       <c r="B13" t="n">
-        <v>90545</v>
+        <v>97953</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1876,26 +1891,27 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>219847</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1903,10 +1919,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>454188</v>
+        <v>454190</v>
       </c>
       <c r="R13" t="n">
-        <v>7169986</v>
+        <v>7170110</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1939,11 +1955,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-08-18</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>På granhögstubbe.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1971,10 +1982,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120046564</v>
+        <v>120046869</v>
       </c>
       <c r="B14" t="n">
-        <v>91565</v>
+        <v>97930</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1983,30 +1994,31 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5836</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Guldkremla</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Russula aurea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Pers.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2014,10 +2026,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>454274</v>
+        <v>454180</v>
       </c>
       <c r="R14" t="n">
-        <v>7170002</v>
+        <v>7170065</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2077,10 +2089,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120046420</v>
+        <v>120046880</v>
       </c>
       <c r="B15" t="n">
-        <v>78542</v>
+        <v>97951</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2089,30 +2101,31 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2120,10 +2133,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>454365</v>
+        <v>454180</v>
       </c>
       <c r="R15" t="n">
-        <v>7169956</v>
+        <v>7170065</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2156,11 +2169,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-08-18</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På gammal björk.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2188,10 +2196,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120046446</v>
+        <v>120046486</v>
       </c>
       <c r="B16" t="n">
-        <v>78542</v>
+        <v>94334</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2200,30 +2208,31 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2231,10 +2240,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>454357</v>
+        <v>454316</v>
       </c>
       <c r="R16" t="n">
-        <v>7169950</v>
+        <v>7169955</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2267,11 +2276,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-08-18</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På grangrenar.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2299,10 +2303,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120046720</v>
+        <v>120046702</v>
       </c>
       <c r="B17" t="n">
-        <v>90576</v>
+        <v>78542</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2315,21 +2319,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2342,10 +2346,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>454158</v>
+        <v>454157</v>
       </c>
       <c r="R17" t="n">
-        <v>7169997</v>
+        <v>7169992</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2382,7 +2386,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På torrgran.</t>
+          <t>På grangrenar.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2410,10 +2414,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120046814</v>
+        <v>120046845</v>
       </c>
       <c r="B18" t="n">
-        <v>78542</v>
+        <v>93766</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2422,30 +2426,31 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>2412</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Källmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Philonotis fontana</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2453,10 +2458,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>454172</v>
+        <v>454168</v>
       </c>
       <c r="R18" t="n">
-        <v>7170015</v>
+        <v>7170020</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2489,11 +2494,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-08-18</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På grangrenar.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2521,10 +2521,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120046702</v>
+        <v>120046632</v>
       </c>
       <c r="B19" t="n">
-        <v>78542</v>
+        <v>97847</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2533,30 +2533,31 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2564,10 +2565,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>454157</v>
+        <v>454185</v>
       </c>
       <c r="R19" t="n">
-        <v>7169992</v>
+        <v>7169988</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2600,11 +2601,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-08-18</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På grangrenar.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2632,10 +2628,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120046554</v>
+        <v>120046472</v>
       </c>
       <c r="B20" t="n">
-        <v>79652</v>
+        <v>97951</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2648,26 +2644,27 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6462</v>
+        <v>221952</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2675,10 +2672,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>454274</v>
+        <v>454355</v>
       </c>
       <c r="R20" t="n">
-        <v>7170002</v>
+        <v>7169944</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2711,11 +2708,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-08-18</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>På klen rönn.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2743,10 +2735,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120046876</v>
+        <v>120046587</v>
       </c>
       <c r="B21" t="n">
-        <v>97829</v>
+        <v>91512</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2759,27 +2751,26 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219795</v>
+        <v>4769</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2787,10 +2778,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>454180</v>
+        <v>454254</v>
       </c>
       <c r="R21" t="n">
-        <v>7170065</v>
+        <v>7169982</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2850,10 +2841,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120046587</v>
+        <v>120046814</v>
       </c>
       <c r="B22" t="n">
-        <v>91512</v>
+        <v>78542</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2862,25 +2853,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4769</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2893,10 +2884,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>454254</v>
+        <v>454172</v>
       </c>
       <c r="R22" t="n">
-        <v>7169982</v>
+        <v>7170015</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2929,6 +2920,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-08-18</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>På grangrenar.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2956,10 +2952,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120046845</v>
+        <v>120046765</v>
       </c>
       <c r="B23" t="n">
-        <v>93766</v>
+        <v>90598</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2968,31 +2964,30 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2412</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Källmossa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Philonotis fontana</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3000,10 +2995,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>454168</v>
+        <v>454176</v>
       </c>
       <c r="R23" t="n">
-        <v>7170020</v>
+        <v>7170001</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3036,6 +3031,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-08-18</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>På granlåga.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3063,10 +3063,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120046671</v>
+        <v>120046602</v>
       </c>
       <c r="B24" t="n">
-        <v>79652</v>
+        <v>90545</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3079,21 +3079,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6462</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3106,10 +3106,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>454160</v>
+        <v>454188</v>
       </c>
       <c r="R24" t="n">
-        <v>7169971</v>
+        <v>7169986</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3146,7 +3146,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På rönn.</t>
+          <t>På granhögstubbe.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3174,10 +3174,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120046765</v>
+        <v>120046876</v>
       </c>
       <c r="B25" t="n">
-        <v>90598</v>
+        <v>97829</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3186,30 +3186,31 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>219795</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3217,10 +3218,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>454176</v>
+        <v>454180</v>
       </c>
       <c r="R25" t="n">
-        <v>7170001</v>
+        <v>7170065</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3253,11 +3254,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-08-18</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>På granlåga.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3285,10 +3281,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120046869</v>
+        <v>120046676</v>
       </c>
       <c r="B26" t="n">
-        <v>97930</v>
+        <v>74659</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3297,31 +3293,30 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>1467</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3329,10 +3324,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>454180</v>
+        <v>454160</v>
       </c>
       <c r="R26" t="n">
-        <v>7170065</v>
+        <v>7169971</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3365,6 +3360,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-08-18</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>På högstubbe av björk.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3392,10 +3392,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120046528</v>
+        <v>120046842</v>
       </c>
       <c r="B27" t="n">
-        <v>97829</v>
+        <v>94274</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3408,21 +3408,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>219795</v>
+        <v>756</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Käppkrokmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Hamatocaulis vernicosus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
+          <t>(Mitt.) Hedenäs</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3436,10 +3436,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>454297</v>
+        <v>454168</v>
       </c>
       <c r="R27" t="n">
-        <v>7169982</v>
+        <v>7170020</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>

--- a/artfynd/A 47636-2022 artfynd.xlsx
+++ b/artfynd/A 47636-2022 artfynd.xlsx
@@ -3499,10 +3499,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122746310</v>
+        <v>122746311</v>
       </c>
       <c r="B28" t="n">
-        <v>94176</v>
+        <v>105446</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3515,34 +3515,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1004672</v>
+        <v>221725</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Källmossor</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Philonotis</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Brid.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Andersstugan NÖ, Jmt</t>
+          <t>Göktjärnen NV, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>454173</v>
+        <v>454186</v>
       </c>
       <c r="R28" t="n">
-        <v>7169967</v>
+        <v>7169972</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3605,10 +3605,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122746311</v>
+        <v>122746313</v>
       </c>
       <c r="B29" t="n">
-        <v>105438</v>
+        <v>79813</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3621,34 +3621,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221725</v>
+        <v>229748</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Göktjärnen NV, Jmt</t>
+          <t>Göktjärnen V, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>454186</v>
+        <v>454254</v>
       </c>
       <c r="R29" t="n">
-        <v>7169972</v>
+        <v>7169976</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3711,10 +3711,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122746312</v>
+        <v>122746310</v>
       </c>
       <c r="B30" t="n">
-        <v>78925</v>
+        <v>94184</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3723,38 +3723,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1249</v>
+        <v>1004672</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Källmossor</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Philonotis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>Brid.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Göktjärnen V, Jmt</t>
+          <t>Andersstugan NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>454217</v>
+        <v>454173</v>
       </c>
       <c r="R30" t="n">
-        <v>7169965</v>
+        <v>7169967</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3817,10 +3817,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122746313</v>
+        <v>122746312</v>
       </c>
       <c r="B31" t="n">
-        <v>79809</v>
+        <v>78929</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3829,25 +3829,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>229748</v>
+        <v>1249</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3857,10 +3857,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>454254</v>
+        <v>454217</v>
       </c>
       <c r="R31" t="n">
-        <v>7169976</v>
+        <v>7169965</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>

--- a/artfynd/A 47636-2022 artfynd.xlsx
+++ b/artfynd/A 47636-2022 artfynd.xlsx
@@ -3499,10 +3499,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122746311</v>
+        <v>122746312</v>
       </c>
       <c r="B28" t="n">
-        <v>105446</v>
+        <v>78929</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3511,38 +3511,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221725</v>
+        <v>1249</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Göktjärnen NV, Jmt</t>
+          <t>Göktjärnen V, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>454186</v>
+        <v>454217</v>
       </c>
       <c r="R28" t="n">
-        <v>7169972</v>
+        <v>7169965</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3711,10 +3711,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122746310</v>
+        <v>122746311</v>
       </c>
       <c r="B30" t="n">
-        <v>94184</v>
+        <v>105446</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3727,34 +3727,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1004672</v>
+        <v>221725</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Källmossor</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Philonotis</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Brid.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Andersstugan NÖ, Jmt</t>
+          <t>Göktjärnen NV, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>454173</v>
+        <v>454186</v>
       </c>
       <c r="R30" t="n">
-        <v>7169967</v>
+        <v>7169972</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3817,10 +3817,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122746312</v>
+        <v>122746310</v>
       </c>
       <c r="B31" t="n">
-        <v>78929</v>
+        <v>94184</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3829,38 +3829,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1249</v>
+        <v>1004672</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Källmossor</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Philonotis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>Brid.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Göktjärnen V, Jmt</t>
+          <t>Andersstugan NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>454217</v>
+        <v>454173</v>
       </c>
       <c r="R31" t="n">
-        <v>7169965</v>
+        <v>7169967</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>

--- a/artfynd/A 47636-2022 artfynd.xlsx
+++ b/artfynd/A 47636-2022 artfynd.xlsx
@@ -3499,10 +3499,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122746312</v>
+        <v>122746313</v>
       </c>
       <c r="B28" t="n">
-        <v>78929</v>
+        <v>79813</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3511,25 +3511,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1249</v>
+        <v>229748</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3539,10 +3539,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>454217</v>
+        <v>454254</v>
       </c>
       <c r="R28" t="n">
-        <v>7169965</v>
+        <v>7169976</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3605,10 +3605,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122746313</v>
+        <v>122746310</v>
       </c>
       <c r="B29" t="n">
-        <v>79813</v>
+        <v>94186</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3621,34 +3621,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>229748</v>
+        <v>1004672</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Källmossor</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Philonotis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>Brid.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Göktjärnen V, Jmt</t>
+          <t>Andersstugan NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>454254</v>
+        <v>454173</v>
       </c>
       <c r="R29" t="n">
-        <v>7169976</v>
+        <v>7169967</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3714,7 +3714,7 @@
         <v>122746311</v>
       </c>
       <c r="B30" t="n">
-        <v>105446</v>
+        <v>105448</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3817,10 +3817,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122746310</v>
+        <v>122746312</v>
       </c>
       <c r="B31" t="n">
-        <v>94184</v>
+        <v>78929</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3829,38 +3829,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1004672</v>
+        <v>1249</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Källmossor</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Philonotis</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Brid.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Andersstugan NÖ, Jmt</t>
+          <t>Göktjärnen V, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>454173</v>
+        <v>454217</v>
       </c>
       <c r="R31" t="n">
-        <v>7169967</v>
+        <v>7169965</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>

--- a/artfynd/A 47636-2022 artfynd.xlsx
+++ b/artfynd/A 47636-2022 artfynd.xlsx
@@ -3499,10 +3499,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122746313</v>
+        <v>122746311</v>
       </c>
       <c r="B28" t="n">
-        <v>79813</v>
+        <v>105456</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3515,34 +3515,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>229748</v>
+        <v>221725</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Göktjärnen V, Jmt</t>
+          <t>Göktjärnen NV, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>454254</v>
+        <v>454186</v>
       </c>
       <c r="R28" t="n">
-        <v>7169976</v>
+        <v>7169972</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3605,10 +3605,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122746310</v>
+        <v>122746312</v>
       </c>
       <c r="B29" t="n">
-        <v>94186</v>
+        <v>78929</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3617,38 +3617,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1004672</v>
+        <v>1249</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Källmossor</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Philonotis</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Brid.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Andersstugan NÖ, Jmt</t>
+          <t>Göktjärnen V, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>454173</v>
+        <v>454217</v>
       </c>
       <c r="R29" t="n">
-        <v>7169967</v>
+        <v>7169965</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3711,10 +3711,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122746311</v>
+        <v>122746310</v>
       </c>
       <c r="B30" t="n">
-        <v>105448</v>
+        <v>94194</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3727,34 +3727,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221725</v>
+        <v>1004672</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Källmossor</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Philonotis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>Brid.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Göktjärnen NV, Jmt</t>
+          <t>Andersstugan NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>454186</v>
+        <v>454173</v>
       </c>
       <c r="R30" t="n">
-        <v>7169972</v>
+        <v>7169967</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3817,10 +3817,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122746312</v>
+        <v>122746313</v>
       </c>
       <c r="B31" t="n">
-        <v>78929</v>
+        <v>79813</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3829,25 +3829,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1249</v>
+        <v>229748</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3857,10 +3857,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>454217</v>
+        <v>454254</v>
       </c>
       <c r="R31" t="n">
-        <v>7169965</v>
+        <v>7169976</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>

--- a/artfynd/A 47636-2022 artfynd.xlsx
+++ b/artfynd/A 47636-2022 artfynd.xlsx
@@ -3499,10 +3499,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122746311</v>
+        <v>122746312</v>
       </c>
       <c r="B28" t="n">
-        <v>105456</v>
+        <v>78925</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3511,38 +3511,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221725</v>
+        <v>1249</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Göktjärnen NV, Jmt</t>
+          <t>Göktjärnen V, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>454186</v>
+        <v>454217</v>
       </c>
       <c r="R28" t="n">
-        <v>7169972</v>
+        <v>7169965</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3605,10 +3605,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122746312</v>
+        <v>122746310</v>
       </c>
       <c r="B29" t="n">
-        <v>78929</v>
+        <v>94194</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3617,38 +3617,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1249</v>
+        <v>1004672</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Källmossor</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Philonotis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>Brid.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Göktjärnen V, Jmt</t>
+          <t>Andersstugan NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>454217</v>
+        <v>454173</v>
       </c>
       <c r="R29" t="n">
-        <v>7169965</v>
+        <v>7169967</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3711,10 +3711,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122746310</v>
+        <v>122746311</v>
       </c>
       <c r="B30" t="n">
-        <v>94194</v>
+        <v>105456</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3727,34 +3727,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1004672</v>
+        <v>221725</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Källmossor</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Philonotis</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Brid.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Andersstugan NÖ, Jmt</t>
+          <t>Göktjärnen NV, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>454173</v>
+        <v>454186</v>
       </c>
       <c r="R30" t="n">
-        <v>7169967</v>
+        <v>7169972</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>

--- a/artfynd/A 47636-2022 artfynd.xlsx
+++ b/artfynd/A 47636-2022 artfynd.xlsx
@@ -3605,10 +3605,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122746310</v>
+        <v>122746311</v>
       </c>
       <c r="B29" t="n">
-        <v>94194</v>
+        <v>105456</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3621,34 +3621,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1004672</v>
+        <v>221725</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Källmossor</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Philonotis</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Brid.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Andersstugan NÖ, Jmt</t>
+          <t>Göktjärnen NV, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>454173</v>
+        <v>454186</v>
       </c>
       <c r="R29" t="n">
-        <v>7169967</v>
+        <v>7169972</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3711,10 +3711,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122746311</v>
+        <v>122746310</v>
       </c>
       <c r="B30" t="n">
-        <v>105456</v>
+        <v>94194</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3727,34 +3727,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221725</v>
+        <v>1004672</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Källmossor</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Philonotis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>Brid.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Göktjärnen NV, Jmt</t>
+          <t>Andersstugan NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>454186</v>
+        <v>454173</v>
       </c>
       <c r="R30" t="n">
-        <v>7169972</v>
+        <v>7169967</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>

--- a/artfynd/A 47636-2022 artfynd.xlsx
+++ b/artfynd/A 47636-2022 artfynd.xlsx
@@ -3499,10 +3499,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122746312</v>
+        <v>122746313</v>
       </c>
       <c r="B28" t="n">
-        <v>78925</v>
+        <v>79813</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3511,25 +3511,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1249</v>
+        <v>229748</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3539,10 +3539,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>454217</v>
+        <v>454254</v>
       </c>
       <c r="R28" t="n">
-        <v>7169965</v>
+        <v>7169976</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3605,10 +3605,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122746311</v>
+        <v>122746310</v>
       </c>
       <c r="B29" t="n">
-        <v>105456</v>
+        <v>94194</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3621,34 +3621,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221725</v>
+        <v>1004672</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Källmossor</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Philonotis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>Brid.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Göktjärnen NV, Jmt</t>
+          <t>Andersstugan NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>454186</v>
+        <v>454173</v>
       </c>
       <c r="R29" t="n">
-        <v>7169972</v>
+        <v>7169967</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3711,10 +3711,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122746310</v>
+        <v>122746312</v>
       </c>
       <c r="B30" t="n">
-        <v>94194</v>
+        <v>78925</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3723,38 +3723,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1004672</v>
+        <v>1249</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Källmossor</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Philonotis</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Brid.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Andersstugan NÖ, Jmt</t>
+          <t>Göktjärnen V, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>454173</v>
+        <v>454217</v>
       </c>
       <c r="R30" t="n">
-        <v>7169967</v>
+        <v>7169965</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3817,10 +3817,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122746313</v>
+        <v>122746311</v>
       </c>
       <c r="B31" t="n">
-        <v>79813</v>
+        <v>105456</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3833,34 +3833,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>229748</v>
+        <v>221725</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Göktjärnen V, Jmt</t>
+          <t>Göktjärnen NV, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>454254</v>
+        <v>454186</v>
       </c>
       <c r="R31" t="n">
-        <v>7169976</v>
+        <v>7169972</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>

--- a/artfynd/A 47636-2022 artfynd.xlsx
+++ b/artfynd/A 47636-2022 artfynd.xlsx
@@ -3605,10 +3605,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122746310</v>
+        <v>122746312</v>
       </c>
       <c r="B29" t="n">
-        <v>94194</v>
+        <v>78925</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3617,38 +3617,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1004672</v>
+        <v>1249</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Källmossor</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Philonotis</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Brid.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Andersstugan NÖ, Jmt</t>
+          <t>Göktjärnen V, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>454173</v>
+        <v>454217</v>
       </c>
       <c r="R29" t="n">
-        <v>7169967</v>
+        <v>7169965</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3711,10 +3711,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122746312</v>
+        <v>122746310</v>
       </c>
       <c r="B30" t="n">
-        <v>78925</v>
+        <v>94194</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3723,38 +3723,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1249</v>
+        <v>1004672</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Källmossor</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Philonotis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>Brid.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Göktjärnen V, Jmt</t>
+          <t>Andersstugan NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>454217</v>
+        <v>454173</v>
       </c>
       <c r="R30" t="n">
-        <v>7169965</v>
+        <v>7169967</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>

--- a/artfynd/A 47636-2022 artfynd.xlsx
+++ b/artfynd/A 47636-2022 artfynd.xlsx
@@ -3499,10 +3499,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122746313</v>
+        <v>122746311</v>
       </c>
       <c r="B28" t="n">
-        <v>79813</v>
+        <v>105459</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3515,34 +3515,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>229748</v>
+        <v>221725</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Göktjärnen V, Jmt</t>
+          <t>Göktjärnen NV, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>454254</v>
+        <v>454186</v>
       </c>
       <c r="R28" t="n">
-        <v>7169976</v>
+        <v>7169972</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3605,10 +3605,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122746312</v>
+        <v>122746310</v>
       </c>
       <c r="B29" t="n">
-        <v>78925</v>
+        <v>94197</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3617,38 +3617,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1249</v>
+        <v>1004672</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Källmossor</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Philonotis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>Brid.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Göktjärnen V, Jmt</t>
+          <t>Andersstugan NÖ, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>454217</v>
+        <v>454173</v>
       </c>
       <c r="R29" t="n">
-        <v>7169965</v>
+        <v>7169967</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3711,10 +3711,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122746310</v>
+        <v>122746313</v>
       </c>
       <c r="B30" t="n">
-        <v>94194</v>
+        <v>79816</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3727,34 +3727,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1004672</v>
+        <v>229748</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Källmossor</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Philonotis</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Brid.</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Andersstugan NÖ, Jmt</t>
+          <t>Göktjärnen V, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>454173</v>
+        <v>454254</v>
       </c>
       <c r="R30" t="n">
-        <v>7169967</v>
+        <v>7169976</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3817,10 +3817,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122746311</v>
+        <v>122746312</v>
       </c>
       <c r="B31" t="n">
-        <v>105456</v>
+        <v>78928</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3829,38 +3829,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221725</v>
+        <v>1249</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Göktjärnen NV, Jmt</t>
+          <t>Göktjärnen V, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>454186</v>
+        <v>454217</v>
       </c>
       <c r="R31" t="n">
-        <v>7169972</v>
+        <v>7169965</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>

--- a/artfynd/A 47636-2022 artfynd.xlsx
+++ b/artfynd/A 47636-2022 artfynd.xlsx
@@ -3502,7 +3502,7 @@
         <v>122746311</v>
       </c>
       <c r="B28" t="n">
-        <v>105459</v>
+        <v>105461</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3608,7 +3608,7 @@
         <v>122746310</v>
       </c>
       <c r="B29" t="n">
-        <v>94197</v>
+        <v>94199</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3714,7 +3714,7 @@
         <v>122746313</v>
       </c>
       <c r="B30" t="n">
-        <v>79816</v>
+        <v>79818</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3820,7 +3820,7 @@
         <v>122746312</v>
       </c>
       <c r="B31" t="n">
-        <v>78928</v>
+        <v>78930</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>

--- a/artfynd/A 47636-2022 artfynd.xlsx
+++ b/artfynd/A 47636-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY118"/>
+  <dimension ref="A1:AZ118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -776,6 +781,11 @@
       <c r="AY2" t="inlineStr">
         <is>
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131736353</t>
         </is>
       </c>
     </row>
@@ -880,6 +890,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120046842</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -986,6 +1001,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120046720</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1092,6 +1112,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131735787</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1198,6 +1223,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131735923</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1304,6 +1334,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131735924</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1405,6 +1440,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122746312</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1511,6 +1551,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737295</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1617,6 +1662,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737296</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1723,6 +1773,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737298</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1829,6 +1884,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737299</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1935,6 +1995,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737300</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2041,6 +2106,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737301</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2140,6 +2210,11 @@
       <c r="AY15" t="inlineStr">
         <is>
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131732298</t>
         </is>
       </c>
     </row>
@@ -2248,6 +2323,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120046676</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2354,6 +2434,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131736891</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2458,6 +2543,11 @@
       <c r="AY18" t="inlineStr">
         <is>
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131736892</t>
         </is>
       </c>
     </row>
@@ -2566,6 +2656,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120046668</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2672,6 +2767,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131736618</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2778,6 +2878,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131736620</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2884,6 +2989,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131736621</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2990,6 +3100,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131736623</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3091,6 +3206,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131736662</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3192,6 +3312,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131736663</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3291,6 +3416,11 @@
       <c r="AY26" t="inlineStr">
         <is>
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131736664</t>
         </is>
       </c>
     </row>
@@ -3395,6 +3525,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120046845</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3497,6 +3632,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120046486</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3603,6 +3743,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737524</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3709,6 +3854,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737527</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3810,6 +3960,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737528</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3911,6 +4066,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737529</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4017,6 +4177,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131734487</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4116,6 +4281,11 @@
       <c r="AY34" t="inlineStr">
         <is>
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131732435</t>
         </is>
       </c>
     </row>
@@ -4219,6 +4389,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120046587</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4325,6 +4500,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120046602</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4426,6 +4606,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131738821</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4525,6 +4710,11 @@
       <c r="AY38" t="inlineStr">
         <is>
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131738822</t>
         </is>
       </c>
     </row>
@@ -4628,6 +4818,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120046564</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4734,6 +4929,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120046420</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4840,6 +5040,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120046446</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4946,6 +5151,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120046702</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5052,6 +5262,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120046814</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5158,6 +5373,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131731617</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5264,6 +5484,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131731618</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5370,6 +5595,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131731620</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5476,6 +5706,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131731621</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5582,6 +5817,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131731622</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5688,6 +5928,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131735811</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5787,6 +6032,11 @@
       <c r="AY50" t="inlineStr">
         <is>
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131740737</t>
         </is>
       </c>
     </row>
@@ -5895,6 +6145,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120046554</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6001,6 +6256,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120046671</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6107,6 +6367,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131740471</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6213,6 +6478,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131740476</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6319,6 +6589,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131740479</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6425,6 +6700,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131740480</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6531,6 +6811,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131740481</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6632,6 +6917,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131732993</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6733,6 +7023,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131734236</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6832,6 +7127,11 @@
       <c r="AY60" t="inlineStr">
         <is>
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131734238</t>
         </is>
       </c>
     </row>
@@ -6936,6 +7236,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120046632</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7035,6 +7340,11 @@
       <c r="AY62" t="inlineStr">
         <is>
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131732424</t>
         </is>
       </c>
     </row>
@@ -7139,6 +7449,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120046528</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7241,6 +7556,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120046876</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7343,6 +7663,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120046948</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7445,6 +7770,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120046421</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7551,6 +7881,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131734440</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7652,6 +7987,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131734443</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7753,6 +8093,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131734444</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7854,6 +8199,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131734554</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7960,6 +8310,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131734336</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8061,6 +8416,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131734337</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8167,6 +8527,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131734338</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8273,6 +8638,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131734340</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8379,6 +8749,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131734341</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8480,6 +8855,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131734342</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8586,6 +8966,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131734343</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8685,6 +9070,11 @@
       <c r="AY78" t="inlineStr">
         <is>
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131734344</t>
         </is>
       </c>
     </row>
@@ -8789,6 +9179,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120046869</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8899,6 +9294,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131735216</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9009,6 +9409,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131735217</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9115,6 +9520,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131734227</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9216,6 +9626,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131739998</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9320,6 +9735,11 @@
       <c r="AY84" t="inlineStr">
         <is>
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131740015</t>
         </is>
       </c>
     </row>
@@ -9424,6 +9844,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120046626</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9525,6 +9950,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122746311</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9626,6 +10056,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131740584</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9732,6 +10167,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131740586</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9833,6 +10273,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131740587</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9937,6 +10382,11 @@
       <c r="AY90" t="inlineStr">
         <is>
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131740588</t>
         </is>
       </c>
     </row>
@@ -10041,6 +10491,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120046472</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10143,6 +10598,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120046580</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10245,6 +10705,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120046880</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10346,6 +10811,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131736414</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10447,6 +10917,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131736415</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10548,6 +11023,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131736666</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10649,6 +11129,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131736667</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10750,6 +11235,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131736668</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10851,6 +11341,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131736670</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10952,6 +11447,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131736672</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11053,6 +11553,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131736673</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11154,6 +11659,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737386</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11255,6 +11765,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737388</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11356,6 +11871,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737389</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11457,6 +11977,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737390</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11558,6 +12083,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737391</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11659,6 +12189,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122746313</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11760,6 +12295,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122746310</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11861,6 +12401,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131734418</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -11962,6 +12507,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131734419</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -12061,6 +12611,11 @@
       <c r="AY111" t="inlineStr">
         <is>
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131734420</t>
         </is>
       </c>
     </row>
@@ -12177,6 +12732,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737003</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -12283,6 +12843,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737293</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -12389,6 +12954,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737294</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12495,6 +13065,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131740474</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -12601,6 +13176,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131740475</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -12705,6 +13285,11 @@
       <c r="AY117" t="inlineStr">
         <is>
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131734339</t>
         </is>
       </c>
     </row>
@@ -12836,8 +13421,132 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737002</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>